--- a/data/CaterNow_Data_master.xlsx
+++ b/data/CaterNow_Data_master.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benedicthorbelt/Documents/Github/uni-caternow-booking-service/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benedicthorbelt/Documents/Github/uni-caternow-booking-service/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9492AAA4-D3AA-314A-B3D4-D828EC2C675B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180873C9-77AB-9F42-8127-28EA097C4BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="15960" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="27840" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vorspeisen" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="282">
   <si>
     <t>productTitle</t>
   </si>
@@ -502,13 +502,7 @@
     <t>Mini Obststicks</t>
   </si>
   <si>
-    <t>Frische Obststücke am Spieß.</t>
-  </si>
-  <si>
     <t>Roastbeefröllchen mit Cornichons</t>
-  </si>
-  <si>
-    <t>Zarte Roastbeefröllchen mit knackigen Cornichons.</t>
   </si>
   <si>
     <t>Mini Franzbrötchen</t>
@@ -517,49 +511,25 @@
     <t>Toskanischer Tomatensalat mit Mozzarella</t>
   </si>
   <si>
-    <t>Tomatensalat mit Mozzarella und gerösteten Nüssen.</t>
-  </si>
-  <si>
     <t>Ziegenkäse mit Süßkartoffelcreme</t>
-  </si>
-  <si>
-    <t>Ziegenkäse auf Süßkartoffelcreme und Wan-Tan-Chip.</t>
   </si>
   <si>
     <t>Petersiliencouscous</t>
   </si>
   <si>
-    <t>Couscous mit Kräutern, Minze, Granatapfel und Joghurt.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Burrata mit Crispy Chili Öl </t>
-  </si>
-  <si>
-    <t>Cremige Burrata mit Crispy  Chili-Öl.</t>
   </si>
   <si>
     <t>Crostini mit Ziegenfrischkäse</t>
   </si>
   <si>
-    <t>Knuspriges Crostini mit Ziegenfrischkäse.</t>
-  </si>
-  <si>
     <t>Geschichteter Blini mit Zitronenschmand</t>
-  </si>
-  <si>
-    <t>Mille Feuille Blini mit Schmandcreme.</t>
   </si>
   <si>
     <t>Kichererbsensalat Greek Style</t>
   </si>
   <si>
-    <t>Kichererbsensalat mit Zitronen-Gurkenjoghurt.</t>
-  </si>
-  <si>
     <t>Roastbeefscheiben mit Remouladensauce</t>
-  </si>
-  <si>
-    <t>Zarte Roastbeefscheiben mit cremiger Remoulade und feiner Eigelberde.</t>
   </si>
   <si>
     <t>a,c</t>
@@ -568,13 +538,7 @@
     <t>Smokey Chicken mit Baba Ganoush</t>
   </si>
   <si>
-    <t>Geräuchertes Hähnchen mit aromatischem Auberginenpüree.</t>
-  </si>
-  <si>
     <t>Shrimps Cocktail mit Avocado</t>
-  </si>
-  <si>
-    <t>Klassiker mit frischen Shrimps und cremiger Avocado.</t>
   </si>
   <si>
     <t>b</t>
@@ -583,16 +547,10 @@
     <t>Lachssashimi mit Gochujang Vinaigrette</t>
   </si>
   <si>
-    <t>Zartes Lachssashimi mit würziger Gochujang-Vinaigrette.</t>
-  </si>
-  <si>
     <t>d</t>
   </si>
   <si>
     <t>Lachscrepeschnitte mit Dill</t>
-  </si>
-  <si>
-    <t>Feine Crepeschnitte mit Lachs und frischem Dill.</t>
   </si>
   <si>
     <t>a,d</t>
@@ -601,13 +559,7 @@
     <t>Kartoffelrösti mit Rauchlachstatar</t>
   </si>
   <si>
-    <t>Knuspriger Rösti mit würzigem Rauchlachstatar.</t>
-  </si>
-  <si>
     <t>Vitello auf Parmesancreme</t>
-  </si>
-  <si>
-    <t>Rosa Kalbfleisch auf Parmesancreme mit Pumpernickelerde.</t>
   </si>
   <si>
     <t>dishType</t>
@@ -626,9 +578,6 @@
   </si>
   <si>
     <t>Häppchen &amp; Fingerfood</t>
-  </si>
-  <si>
-    <t>Fleisch</t>
   </si>
   <si>
     <t>Vegetarisch</t>
@@ -702,6 +651,237 @@
   <si>
     <t>Bratapfelmousse (ohne Rosinen)</t>
   </si>
+  <si>
+    <t>heavy_score</t>
+  </si>
+  <si>
+    <t>filling_score</t>
+  </si>
+  <si>
+    <t>traditional_score</t>
+  </si>
+  <si>
+    <t>Hähnchen</t>
+  </si>
+  <si>
+    <t>Rind</t>
+  </si>
+  <si>
+    <t>Meeresfrüchte</t>
+  </si>
+  <si>
+    <t>Fisch</t>
+  </si>
+  <si>
+    <t>Kalb</t>
+  </si>
+  <si>
+    <t>Geflügel</t>
+  </si>
+  <si>
+    <t>Frische Obststücke am Spieß,</t>
+  </si>
+  <si>
+    <t>Zarte Roastbeefröllchen mit knackigen Cornichons,</t>
+  </si>
+  <si>
+    <t>Tomatensalat mit Mozzarella und gerösteten Nüssen,</t>
+  </si>
+  <si>
+    <t>Ziegenkäse auf Süßkartoffelcreme und Wan-Tan-Chip,</t>
+  </si>
+  <si>
+    <t>Couscous mit Kräutern, Minze, Granatapfel und Joghurt,</t>
+  </si>
+  <si>
+    <t>Cremige Burrata mit Crispy  Chili-Öl,</t>
+  </si>
+  <si>
+    <t>Knuspriges Crostini mit Ziegenfrischkäse,</t>
+  </si>
+  <si>
+    <t>Mille Feuille Blini mit Schmandcreme,</t>
+  </si>
+  <si>
+    <t>Kichererbsensalat mit Zitronen-Gurkenjoghurt,</t>
+  </si>
+  <si>
+    <t>Zarte Roastbeefscheiben mit cremiger Remoulade und feiner Eigelberde,</t>
+  </si>
+  <si>
+    <t>Geräuchertes Hähnchen mit aromatischem Auberginenpüree,</t>
+  </si>
+  <si>
+    <t>Klassiker mit frischen Shrimps und cremiger Avocado,</t>
+  </si>
+  <si>
+    <t>Zartes Lachssashimi mit würziger Gochujang-Vinaigrette,</t>
+  </si>
+  <si>
+    <t>Feine Crepeschnitte mit Lachs und frischem Dill,</t>
+  </si>
+  <si>
+    <t>Knuspriger Rösti mit würzigem Rauchlachstatar,</t>
+  </si>
+  <si>
+    <t>Rosa Kalbfleisch auf Parmesancreme mit Pumpernickelerde,</t>
+  </si>
+  <si>
+    <t>Saftige Chickenroulade gefüllt mit Spinat, serviert mit Pesto Rosso Kartoffeln und würzigem Ajvar-Paprikagemüse,</t>
+  </si>
+  <si>
+    <t>Zartes Rindergeschnetzeltes in kräftiger Sauce, dazu goldene Butterspätzle,</t>
+  </si>
+  <si>
+    <t>Langsam geschmortes Beef-Gulasch nach Milanese-Art mit cremigem Kartoffel-Parmesanstampf,</t>
+  </si>
+  <si>
+    <t>Zartes Geflügelgeschnetzeltes in Rahmsauce, klassisch serviert mit Butterspätzle,</t>
+  </si>
+  <si>
+    <t>Mediterranes Geflügel mit Röstkartoffeln, Zitronen-Honigkarotten und frischem Kräuterschmand,</t>
+  </si>
+  <si>
+    <t>Würzig mariniertes Jerk Chicken mit cremigem Kartoffelstampf und Rahmkohlrabi,</t>
+  </si>
+  <si>
+    <t>Knusprige Ofengnocchi auf Tomaten-Schafskäsecreme, verfeinert mit frischem Rucola,</t>
+  </si>
+  <si>
+    <t>Herzhaftes Pilzgeschnetzeltes mit Sojastripes, serviert mit Butterspätzle,</t>
+  </si>
+  <si>
+    <t>Bunte Bowl mit Kichererbsen, Couscous, Roter Beete und cremiger Tahinisauce,</t>
+  </si>
+  <si>
+    <t>Aromatisches Asiacurry mit Tofu und lockerem Jasminreis,</t>
+  </si>
+  <si>
+    <t>Vegetarische Auberginen-Moussaka mit mildem Joghurt-Dill-Dip,</t>
+  </si>
+  <si>
+    <t>Würziges Pilzgeschnetzeltes mit Sojastripes auf duftendem Kräuter-Basmati-Reis,</t>
+  </si>
+  <si>
+    <t>Vegane Auberginen-Moussaka mit Raz el Hanout Süßkartoffel, Kichererbsen-Brokkoli-Couscous und veganem Joghurt-Dip,</t>
+  </si>
+  <si>
+    <t>Saftiger Schokoladenbrownie, serviert mit cremiger Vanillesauce,</t>
+  </si>
+  <si>
+    <t>Cremiger Cheesecake auf Keksboden, verfeinert mit frischen Beeren,</t>
+  </si>
+  <si>
+    <t>Frische Zitronen-Cheesecakecreme mit feiner Säure,</t>
+  </si>
+  <si>
+    <t>Luftige Mango-Joghurtmousse mit knusprigen exotischen Streuseln,</t>
+  </si>
+  <si>
+    <t>Cremige Mango-Kokosmousse mit fruchtig-knusprigem Topping,</t>
+  </si>
+  <si>
+    <t>Zartschmelzende Schokoladenmousse mit knuspriger Schokoerde,</t>
+  </si>
+  <si>
+    <t>Fruchtige Beerenmousse mit aromatischen Cassis-Streuseln,</t>
+  </si>
+  <si>
+    <t>Leichte Joghurtcreme mit gemischten Beeren,</t>
+  </si>
+  <si>
+    <t>Fein abgestimmte Erdbeer-Rhabarbermousse mit knusprigem Hafercrumble,</t>
+  </si>
+  <si>
+    <t>Cremige Vanillecreme mit knackigen Schokostückchen,</t>
+  </si>
+  <si>
+    <t>Intensiv-fruchtige Kirschmousse mit leichter Süße,</t>
+  </si>
+  <si>
+    <t>Erfrischende Zitronencreme mit feiner Säure,</t>
+  </si>
+  <si>
+    <t>Moderner Cheesecake mit Ube, Heidelbeeren und verschiedenen Texturen,</t>
+  </si>
+  <si>
+    <t>Kreatives Tiramisu mit Waffeln und frischen Beeren,</t>
+  </si>
+  <si>
+    <t>Klassisches Tiramisu mit Mascarpone und feiner Kaffeenote,</t>
+  </si>
+  <si>
+    <t>Fruchtige Pflaumengrütze mit feiner Rumnote,</t>
+  </si>
+  <si>
+    <t>Cremige Bratapfelmousse mit winterlichen Gewürzen,</t>
+  </si>
+  <si>
+    <t>Flaumiger Germknödel mit fruchtiger Kirschfüllung, warm im Wärmeeinsatz serviert,</t>
+  </si>
+  <si>
+    <t>Warmer Marillenknödel mit fruchtiger Füllung, ideal für den Wärmeeinsatz,</t>
+  </si>
+  <si>
+    <t>Lockerer Kaiserschmarren ohne Rosinen, warm im Wärmeeinsatz serviert,</t>
+  </si>
+  <si>
+    <t>Klassischer Apfelstrudel, warm im Wärmeeinsatz serviert,</t>
+  </si>
+  <si>
+    <t>Frisches saisonales Handobst, ideal portioniert für Meetings und Pausen,</t>
+  </si>
+  <si>
+    <t>Kleine, saftige Muffins in wechselnden Geschmacksrichtungen,</t>
+  </si>
+  <si>
+    <t>Bunte Mini Donuts mit verschiedenen Glasuren,</t>
+  </si>
+  <si>
+    <t>Knusprig-buttrige Mini Croissants, frisch gebacken,</t>
+  </si>
+  <si>
+    <t>Portugiesisches Blätterteiggebäck mit cremiger Puddingfüllung,</t>
+  </si>
+  <si>
+    <t>Blättriges Gebäck nach skandinavischer Art,</t>
+  </si>
+  <si>
+    <t>Zimtiges Hamburger Klassiker-Gebäck im Mini-Format,</t>
+  </si>
+  <si>
+    <t>Knusprige Tartelette mit cremiger Kokos-Panna-Cotta-Füllung,</t>
+  </si>
+  <si>
+    <t>Klassisches Tiramisu mit feiner Kaffeenote,</t>
+  </si>
+  <si>
+    <t>Cremiger Naturjoghurt verfeinert mit aromatischem Honig,</t>
+  </si>
+  <si>
+    <t>Traditionelles Bircher Müsli mit Haferflocken, Apfel und Nüssen,</t>
+  </si>
+  <si>
+    <t>Frischer Obstsalat aus Apfel, Orange und Trauben,</t>
+  </si>
+  <si>
+    <t>Exotischer Fruchtsalat mit Ananas und Kiwi,</t>
+  </si>
+  <si>
+    <t>Fruchtig-frischer Salat aus Orange und Kiwi,</t>
+  </si>
+  <si>
+    <t>Abwechslungsreiche Auswahl an Bio-Blechkuchen,</t>
+  </si>
+  <si>
+    <t>Geschichteter griechischer Joghurt mit Honig, Nüssen und saisonalen Früchten,</t>
+  </si>
+  <si>
+    <t>Luftige Mascarponecreme mit fruchtigem Himbeerpüree,</t>
+  </si>
+  <si>
+    <t>Feincremige Pistazienmousse mit fruchtigem Beerenragout,</t>
+  </si>
 </sst>
 </file>
 
@@ -722,6 +902,7 @@
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -762,7 +943,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -785,11 +966,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="9"/>
+      </left>
+      <right style="thin">
+        <color indexed="9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -839,6 +1031,10 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1972,11 +2168,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X956"/>
+  <dimension ref="A1:X957"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22.33203125" style="1" customWidth="1"/>
-    <col min="2" max="3" width="32.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="29.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.1640625" style="1" customWidth="1"/>
@@ -1996,13 +2193,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -2014,11 +2211,17 @@
         <v>8</v>
       </c>
       <c r="I1" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="L1" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="4"/>
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
@@ -2037,26 +2240,34 @@
         <v>154</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>155</v>
+        <v>214</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>12</v>
+        <v>177</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>182</v>
       </c>
       <c r="F2" s="18">
         <v>2.5</v>
       </c>
       <c r="G2" s="17"/>
       <c r="H2" s="17"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
+      <c r="I2" s="24">
+        <v>0.1</v>
+      </c>
+      <c r="J2" s="24">
+        <v>0.1</v>
+      </c>
+      <c r="K2" s="24">
+        <v>0.1</v>
+      </c>
+      <c r="L2" s="25">
+        <v>0.3</v>
+      </c>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
@@ -2072,29 +2283,37 @@
     </row>
     <row r="3" spans="1:24" ht="13.75" customHeight="1">
       <c r="A3" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>12</v>
+        <v>178</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>209</v>
       </c>
       <c r="F3" s="18">
         <v>2.5</v>
       </c>
       <c r="G3" s="17"/>
       <c r="H3" s="17"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
+      <c r="I3" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="J3" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="K3" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="L3" s="24">
+        <v>0.6</v>
+      </c>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
@@ -2110,19 +2329,19 @@
     </row>
     <row r="4" spans="1:24" ht="13.75" customHeight="1">
       <c r="A4" s="17" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>160</v>
+        <v>216</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>12</v>
+        <v>179</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>181</v>
       </c>
       <c r="F4" s="18">
         <v>3.9</v>
@@ -2133,10 +2352,18 @@
       <c r="H4" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
+      <c r="I4" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="J4" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="K4" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="L4" s="24">
+        <v>0.5</v>
+      </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
@@ -2152,19 +2379,19 @@
     </row>
     <row r="5" spans="1:24" ht="13.75" customHeight="1">
       <c r="A5" s="17" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>12</v>
+        <v>180</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>181</v>
       </c>
       <c r="F5" s="18">
         <v>3.9</v>
@@ -2175,10 +2402,18 @@
       <c r="H5" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
+      <c r="I5" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="J5" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="K5" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="L5" s="24">
+        <v>0.2</v>
+      </c>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
@@ -2194,19 +2429,19 @@
     </row>
     <row r="6" spans="1:24" ht="13.75" customHeight="1">
       <c r="A6" s="17" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>12</v>
+        <v>179</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>181</v>
       </c>
       <c r="F6" s="18">
         <v>3.9</v>
@@ -2217,10 +2452,18 @@
       <c r="H6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
+      <c r="I6" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="J6" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="K6" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="L6" s="24">
+        <v>0.4</v>
+      </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
@@ -2236,19 +2479,19 @@
     </row>
     <row r="7" spans="1:24" ht="13.75" customHeight="1">
       <c r="A7" s="17" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>166</v>
+        <v>219</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>12</v>
+        <v>178</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>181</v>
       </c>
       <c r="F7" s="18">
         <v>3.9</v>
@@ -2259,10 +2502,18 @@
       <c r="H7" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
+      <c r="I7" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="J7" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="K7" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="L7" s="24">
+        <v>0.3</v>
+      </c>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
@@ -2278,19 +2529,19 @@
     </row>
     <row r="8" spans="1:24" ht="13.75" customHeight="1">
       <c r="A8" s="17" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>168</v>
+        <v>220</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>12</v>
+        <v>180</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>181</v>
       </c>
       <c r="F8" s="18">
         <v>3.9</v>
@@ -2301,10 +2552,18 @@
       <c r="H8" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
+      <c r="I8" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="J8" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="K8" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="L8" s="24">
+        <v>0.5</v>
+      </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
@@ -2320,19 +2579,19 @@
     </row>
     <row r="9" spans="1:24" ht="13.75" customHeight="1">
       <c r="A9" s="17" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>170</v>
+        <v>221</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>12</v>
+        <v>180</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>181</v>
       </c>
       <c r="F9" s="18">
         <v>3.9</v>
@@ -2343,10 +2602,18 @@
       <c r="H9" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
+      <c r="I9" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="J9" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="K9" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="L9" s="24">
+        <v>0.4</v>
+      </c>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
@@ -2362,19 +2629,19 @@
     </row>
     <row r="10" spans="1:24" ht="13.75" customHeight="1">
       <c r="A10" s="17" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>172</v>
+        <v>222</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>12</v>
+        <v>179</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>181</v>
       </c>
       <c r="F10" s="18">
         <v>3.9</v>
@@ -2385,10 +2652,18 @@
       <c r="H10" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
+      <c r="I10" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="J10" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="K10" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="L10" s="24">
+        <v>0.4</v>
+      </c>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
@@ -2404,31 +2679,39 @@
     </row>
     <row r="11" spans="1:24" ht="13.75" customHeight="1">
       <c r="A11" s="17" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>12</v>
+        <v>178</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>209</v>
       </c>
       <c r="F11" s="18">
         <v>4.9000000000000004</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
+      <c r="I11" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="J11" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="K11" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="L11" s="24">
+        <v>0.7</v>
+      </c>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
@@ -2444,29 +2727,37 @@
     </row>
     <row r="12" spans="1:24" ht="13.75" customHeight="1">
       <c r="A12" s="17" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>177</v>
+        <v>224</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>12</v>
+        <v>180</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>213</v>
       </c>
       <c r="F12" s="18">
         <v>4.9000000000000004</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
+      <c r="I12" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="J12" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="K12" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="L12" s="24">
+        <v>0.2</v>
+      </c>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
@@ -2482,31 +2773,39 @@
     </row>
     <row r="13" spans="1:24" ht="13.75" customHeight="1">
       <c r="A13" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="D13" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>208</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>12</v>
+      <c r="E13" s="22" t="s">
+        <v>210</v>
       </c>
       <c r="F13" s="18">
         <v>4.9000000000000004</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
+      <c r="I13" s="24">
+        <v>0.7</v>
+      </c>
+      <c r="J13" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="K13" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="L13" s="24">
+        <v>0.7</v>
+      </c>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
@@ -2522,31 +2821,39 @@
     </row>
     <row r="14" spans="1:24" ht="13.75" customHeight="1">
       <c r="A14" s="17" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>182</v>
+        <v>226</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>12</v>
+        <v>178</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>211</v>
       </c>
       <c r="F14" s="18">
         <v>4.9000000000000004</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
+      <c r="I14" s="24">
+        <v>0.8</v>
+      </c>
+      <c r="J14" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="K14" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="L14" s="24">
+        <v>0.1</v>
+      </c>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
@@ -2562,31 +2869,39 @@
     </row>
     <row r="15" spans="1:24" ht="13.75" customHeight="1">
       <c r="A15" s="17" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>185</v>
+        <v>227</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>12</v>
+        <v>180</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>211</v>
       </c>
       <c r="F15" s="18">
         <v>4.9000000000000004</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
+      <c r="I15" s="24">
+        <v>0.7</v>
+      </c>
+      <c r="J15" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="K15" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="L15" s="24">
+        <v>0.5</v>
+      </c>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
@@ -2602,31 +2917,39 @@
     </row>
     <row r="16" spans="1:24" ht="13.75" customHeight="1">
       <c r="A16" s="17" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>12</v>
+        <v>180</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>211</v>
       </c>
       <c r="F16" s="18">
         <v>4.9000000000000004</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
+      <c r="I16" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="J16" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="K16" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="L16" s="24">
+        <v>0.5</v>
+      </c>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
@@ -2642,31 +2965,39 @@
     </row>
     <row r="17" spans="1:24" ht="13.75" customHeight="1">
       <c r="A17" s="17" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>190</v>
+        <v>229</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>12</v>
+        <v>180</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>212</v>
       </c>
       <c r="F17" s="18">
         <v>4.9000000000000004</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
+      <c r="I17" s="24">
+        <v>0.9</v>
+      </c>
+      <c r="J17" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="K17" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="L17" s="24">
+        <v>0.6</v>
+      </c>
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
@@ -2685,14 +3016,14 @@
         <v>9</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>10</v>
+        <v>230</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D18" s="17"/>
       <c r="E18" s="8" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="F18" s="9">
         <v>18</v>
@@ -2703,10 +3034,18 @@
       <c r="H18" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
+      <c r="I18" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="J18" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="K18" s="24">
+        <v>0.7</v>
+      </c>
+      <c r="L18" s="24">
+        <v>0.5</v>
+      </c>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
@@ -2725,14 +3064,14 @@
         <v>15</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>16</v>
+        <v>231</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D19" s="17"/>
       <c r="E19" s="8" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="F19" s="9">
         <v>18</v>
@@ -2743,10 +3082,18 @@
       <c r="H19" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
+      <c r="I19" s="24">
+        <v>0.7</v>
+      </c>
+      <c r="J19" s="24">
+        <v>0.8</v>
+      </c>
+      <c r="K19" s="24">
+        <v>0.8</v>
+      </c>
+      <c r="L19" s="24">
+        <v>0.9</v>
+      </c>
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
@@ -2765,14 +3112,14 @@
         <v>17</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>18</v>
+        <v>232</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D20" s="17"/>
       <c r="E20" s="8" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="F20" s="9">
         <v>15</v>
@@ -2783,10 +3130,18 @@
       <c r="H20" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
+      <c r="I20" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="J20" s="24">
+        <v>0.8</v>
+      </c>
+      <c r="K20" s="26">
+        <v>0.8</v>
+      </c>
+      <c r="L20" s="24">
+        <v>0.8</v>
+      </c>
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
@@ -2805,14 +3160,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D21" s="17"/>
       <c r="E21" s="8" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="F21" s="9">
         <v>15</v>
@@ -2823,10 +3178,18 @@
       <c r="H21" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
+      <c r="I21" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="J21" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="K21" s="24">
+        <v>0.7</v>
+      </c>
+      <c r="L21" s="24">
+        <v>0.8</v>
+      </c>
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
@@ -2845,14 +3208,14 @@
         <v>21</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>22</v>
+        <v>234</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D22" s="17"/>
       <c r="E22" s="8" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="F22" s="9">
         <v>15</v>
@@ -2863,10 +3226,18 @@
       <c r="H22" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
+      <c r="I22" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="J22" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="K22" s="24">
+        <v>0.7</v>
+      </c>
+      <c r="L22" s="24">
+        <v>0.5</v>
+      </c>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
@@ -2885,14 +3256,14 @@
         <v>24</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>25</v>
+        <v>235</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D23" s="17"/>
       <c r="E23" s="8" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="F23" s="9">
         <v>15</v>
@@ -2903,10 +3274,18 @@
       <c r="H23" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
+      <c r="I23" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="J23" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="K23" s="24">
+        <v>0.7</v>
+      </c>
+      <c r="L23" s="24">
+        <v>0.2</v>
+      </c>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
@@ -2925,14 +3304,14 @@
         <v>26</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>27</v>
+        <v>236</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D24" s="17"/>
       <c r="E24" s="8" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="F24" s="9">
         <v>15</v>
@@ -2943,10 +3322,18 @@
       <c r="H24" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
+      <c r="I24" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="J24" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="K24" s="24">
+        <v>0.7</v>
+      </c>
+      <c r="L24" s="24">
+        <v>0.3</v>
+      </c>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
@@ -2965,14 +3352,14 @@
         <v>29</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>30</v>
+        <v>237</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D25" s="17"/>
       <c r="E25" s="8" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="F25" s="9">
         <v>15</v>
@@ -2983,10 +3370,18 @@
       <c r="H25" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
+      <c r="I25" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="J25" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="K25" s="24">
+        <v>0.7</v>
+      </c>
+      <c r="L25" s="24">
+        <v>0.4</v>
+      </c>
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
@@ -3005,14 +3400,14 @@
         <v>32</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>33</v>
+        <v>238</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D26" s="17"/>
       <c r="E26" s="8" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="F26" s="9">
         <v>15</v>
@@ -3023,10 +3418,18 @@
       <c r="H26" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
+      <c r="I26" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="J26" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="K26" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="L26" s="24">
+        <v>0.2</v>
+      </c>
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
@@ -3045,14 +3448,14 @@
         <v>36</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>37</v>
+        <v>239</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D27" s="17"/>
       <c r="E27" s="8" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="F27" s="9">
         <v>15</v>
@@ -3063,10 +3466,18 @@
       <c r="H27" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
+      <c r="I27" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="J27" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="K27" s="24">
+        <v>0.7</v>
+      </c>
+      <c r="L27" s="24">
+        <v>0.1</v>
+      </c>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
@@ -3085,14 +3496,14 @@
         <v>38</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>39</v>
+        <v>240</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="8" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="F28" s="9">
         <v>15</v>
@@ -3103,10 +3514,18 @@
       <c r="H28" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
+      <c r="I28" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="J28" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="K28" s="24">
+        <v>0.7</v>
+      </c>
+      <c r="L28" s="24">
+        <v>0.6</v>
+      </c>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
@@ -3125,14 +3544,14 @@
         <v>40</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>41</v>
+        <v>241</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="8" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="F29" s="9">
         <v>15</v>
@@ -3143,10 +3562,18 @@
       <c r="H29" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
+      <c r="I29" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="J29" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="K29" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="L29" s="24">
+        <v>0.3</v>
+      </c>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
@@ -3165,14 +3592,14 @@
         <v>42</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>43</v>
+        <v>242</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="8" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="F30" s="9">
         <v>18</v>
@@ -3183,10 +3610,18 @@
       <c r="H30" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
+      <c r="I30" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="J30" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="K30" s="24">
+        <v>0.7</v>
+      </c>
+      <c r="L30" s="24">
+        <v>0.4</v>
+      </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
@@ -3205,16 +3640,16 @@
         <v>44</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>45</v>
+        <v>243</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>12</v>
+        <v>181</v>
       </c>
       <c r="F31" s="9">
         <v>3.9</v>
@@ -3225,10 +3660,18 @@
       <c r="H31" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
+      <c r="I31" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="J31" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="K31" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="L31" s="24">
+        <v>0.7</v>
+      </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
@@ -3247,16 +3690,16 @@
         <v>49</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>50</v>
+        <v>244</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>12</v>
+        <v>181</v>
       </c>
       <c r="F32" s="9">
         <v>3.9</v>
@@ -3267,10 +3710,18 @@
       <c r="H32" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
+      <c r="I32" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="J32" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="K32" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="L32" s="24">
+        <v>0.6</v>
+      </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
@@ -3289,16 +3740,16 @@
         <v>51</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>52</v>
+        <v>245</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>12</v>
+        <v>181</v>
       </c>
       <c r="F33" s="9">
         <v>3.9</v>
@@ -3309,10 +3760,18 @@
       <c r="H33" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
+      <c r="I33" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="J33" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="K33" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="L33" s="24">
+        <v>0.4</v>
+      </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
@@ -3331,16 +3790,16 @@
         <v>55</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>12</v>
+        <v>181</v>
       </c>
       <c r="F34" s="9">
         <v>3.9</v>
@@ -3351,10 +3810,18 @@
       <c r="H34" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
+      <c r="I34" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="J34" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="K34" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="L34" s="24">
+        <v>0.1</v>
+      </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
@@ -3373,16 +3840,16 @@
         <v>58</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>59</v>
+        <v>247</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>12</v>
+        <v>182</v>
       </c>
       <c r="F35" s="9">
         <v>3.9</v>
@@ -3393,10 +3860,18 @@
       <c r="H35" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
+      <c r="I35" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="J35" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="K35" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="L35" s="24">
+        <v>0.1</v>
+      </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
@@ -3415,16 +3890,16 @@
         <v>60</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>61</v>
+        <v>248</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>12</v>
+        <v>181</v>
       </c>
       <c r="F36" s="9">
         <v>3.9</v>
@@ -3435,10 +3910,18 @@
       <c r="H36" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
+      <c r="I36" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="J36" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="K36" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="L36" s="24">
+        <v>0.5</v>
+      </c>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
@@ -3457,16 +3940,16 @@
         <v>62</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>63</v>
+        <v>249</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>12</v>
+        <v>181</v>
       </c>
       <c r="F37" s="9">
         <v>3.9</v>
@@ -3477,10 +3960,18 @@
       <c r="H37" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
+      <c r="I37" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="J37" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="K37" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="L37" s="24">
+        <v>0.3</v>
+      </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
       <c r="O37" s="5"/>
@@ -3495,30 +3986,14 @@
       <c r="X37" s="5"/>
     </row>
     <row r="38" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A38" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="9">
-        <v>3.9</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>48</v>
-      </c>
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
@@ -3538,16 +4013,16 @@
     </row>
     <row r="39" spans="1:24" ht="13.75" customHeight="1">
       <c r="A39" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>67</v>
+        <v>250</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>12</v>
@@ -3556,7 +4031,7 @@
         <v>3.9</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="H39" s="8" t="s">
         <v>48</v>
@@ -3580,16 +4055,16 @@
     </row>
     <row r="40" spans="1:24" ht="13.75" customHeight="1">
       <c r="A40" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>69</v>
+        <v>251</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>12</v>
@@ -3598,7 +4073,7 @@
         <v>3.9</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>48</v>
@@ -3622,16 +4097,16 @@
     </row>
     <row r="41" spans="1:24" ht="13.75" customHeight="1">
       <c r="A41" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>71</v>
+        <v>252</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="E41" s="8" t="s">
         <v>12</v>
@@ -3664,16 +4139,16 @@
     </row>
     <row r="42" spans="1:24" ht="13.75" customHeight="1">
       <c r="A42" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>73</v>
+        <v>253</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>12</v>
@@ -3706,16 +4181,16 @@
     </row>
     <row r="43" spans="1:24" ht="13.75" customHeight="1">
       <c r="A43" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>75</v>
+        <v>254</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>12</v>
@@ -3724,7 +4199,7 @@
         <v>3.9</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="H43" s="8" t="s">
         <v>48</v>
@@ -3748,16 +4223,16 @@
     </row>
     <row r="44" spans="1:24" ht="13.75" customHeight="1">
       <c r="A44" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>77</v>
+        <v>255</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>12</v>
@@ -3790,16 +4265,16 @@
     </row>
     <row r="45" spans="1:24" ht="13.75" customHeight="1">
       <c r="A45" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>79</v>
+        <v>256</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>12</v>
@@ -3811,7 +4286,7 @@
         <v>13</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
@@ -3832,16 +4307,16 @@
     </row>
     <row r="46" spans="1:24" ht="13.75" customHeight="1">
       <c r="A46" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>12</v>
@@ -3849,9 +4324,11 @@
       <c r="F46" s="9">
         <v>3.9</v>
       </c>
-      <c r="G46" s="12"/>
+      <c r="G46" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="H46" s="8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
@@ -3872,16 +4349,16 @@
     </row>
     <row r="47" spans="1:24" ht="13.75" customHeight="1">
       <c r="A47" s="8" t="s">
-        <v>221</v>
+        <v>81</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>85</v>
+        <v>258</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>12</v>
@@ -3889,11 +4366,9 @@
       <c r="F47" s="9">
         <v>3.9</v>
       </c>
-      <c r="G47" s="8" t="s">
-        <v>54</v>
-      </c>
+      <c r="G47" s="12"/>
       <c r="H47" s="8" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
@@ -3914,16 +4389,16 @@
     </row>
     <row r="48" spans="1:24" ht="13.75" customHeight="1">
       <c r="A48" s="8" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>87</v>
+        <v>259</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>12</v>
@@ -3932,7 +4407,7 @@
         <v>3.9</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="H48" s="8" t="s">
         <v>48</v>
@@ -3956,16 +4431,16 @@
     </row>
     <row r="49" spans="1:24" ht="13.75" customHeight="1">
       <c r="A49" s="8" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>89</v>
+        <v>260</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>12</v>
@@ -3998,16 +4473,16 @@
     </row>
     <row r="50" spans="1:24" ht="13.75" customHeight="1">
       <c r="A50" s="8" t="s">
-        <v>90</v>
+        <v>197</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>91</v>
+        <v>261</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>12</v>
@@ -4040,16 +4515,16 @@
     </row>
     <row r="51" spans="1:24" ht="13.75" customHeight="1">
       <c r="A51" s="8" t="s">
-        <v>215</v>
+        <v>90</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>93</v>
+        <v>262</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>12</v>
@@ -4082,25 +4557,29 @@
     </row>
     <row r="52" spans="1:24" ht="13.75" customHeight="1">
       <c r="A52" s="8" t="s">
-        <v>94</v>
+        <v>198</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>95</v>
+        <v>263</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F52" s="9">
-        <v>2</v>
-      </c>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
+        <v>3.9</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
       <c r="K52" s="5"/>
@@ -4120,16 +4599,16 @@
     </row>
     <row r="53" spans="1:24" ht="13.75" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>216</v>
+        <v>94</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>101</v>
+        <v>264</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>12</v>
@@ -4137,12 +4616,8 @@
       <c r="F53" s="9">
         <v>2</v>
       </c>
-      <c r="G53" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H53" s="8" t="s">
-        <v>48</v>
-      </c>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
       <c r="I53" s="5"/>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
@@ -4162,16 +4637,16 @@
     </row>
     <row r="54" spans="1:24" ht="13.75" customHeight="1">
       <c r="A54" s="8" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>103</v>
+        <v>265</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>12</v>
@@ -4204,27 +4679,29 @@
     </row>
     <row r="55" spans="1:24" ht="13.75" customHeight="1">
       <c r="A55" s="8" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>109</v>
+        <v>266</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F55" s="9">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G55" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H55" s="12"/>
+      <c r="H55" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
@@ -4244,22 +4721,22 @@
     </row>
     <row r="56" spans="1:24" ht="13.75" customHeight="1">
       <c r="A56" s="8" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>117</v>
+        <v>267</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F56" s="9">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="G56" s="8" t="s">
         <v>13</v>
@@ -4284,16 +4761,16 @@
     </row>
     <row r="57" spans="1:24" ht="13.75" customHeight="1">
       <c r="A57" s="8" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>119</v>
+        <v>268</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>12</v>
@@ -4324,16 +4801,16 @@
     </row>
     <row r="58" spans="1:24" ht="13.75" customHeight="1">
       <c r="A58" s="8" t="s">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>121</v>
+        <v>269</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>12</v>
@@ -4364,16 +4841,16 @@
     </row>
     <row r="59" spans="1:24" ht="13.75" customHeight="1">
       <c r="A59" s="8" t="s">
-        <v>219</v>
+        <v>156</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>123</v>
+        <v>270</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>12</v>
@@ -4382,7 +4859,7 @@
         <v>2.9</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="H59" s="12"/>
       <c r="I59" s="5"/>
@@ -4404,29 +4881,27 @@
     </row>
     <row r="60" spans="1:24" ht="13.75" customHeight="1">
       <c r="A60" s="8" t="s">
-        <v>124</v>
+        <v>202</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>125</v>
+        <v>271</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="E60" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F60" s="9">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H60" s="8" t="s">
-        <v>80</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="H60" s="12"/>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
@@ -4446,16 +4921,16 @@
     </row>
     <row r="61" spans="1:24" ht="13.75" customHeight="1">
       <c r="A61" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>127</v>
+        <v>272</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>12</v>
@@ -4464,9 +4939,11 @@
         <v>3.9</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H61" s="12"/>
+        <v>13</v>
+      </c>
+      <c r="H61" s="8" t="s">
+        <v>80</v>
+      </c>
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
@@ -4486,16 +4963,16 @@
     </row>
     <row r="62" spans="1:24" ht="13.75" customHeight="1">
       <c r="A62" s="8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>130</v>
+        <v>273</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>12</v>
@@ -4504,7 +4981,7 @@
         <v>3.9</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H62" s="12"/>
       <c r="I62" s="5"/>
@@ -4526,16 +5003,16 @@
     </row>
     <row r="63" spans="1:24" ht="13.75" customHeight="1">
       <c r="A63" s="8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>134</v>
+        <v>274</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>12</v>
@@ -4543,7 +5020,9 @@
       <c r="F63" s="9">
         <v>3.9</v>
       </c>
-      <c r="G63" s="12"/>
+      <c r="G63" s="8" t="s">
+        <v>132</v>
+      </c>
       <c r="H63" s="12"/>
       <c r="I63" s="5"/>
       <c r="J63" s="5"/>
@@ -4564,16 +5043,16 @@
     </row>
     <row r="64" spans="1:24" ht="13.75" customHeight="1">
       <c r="A64" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>136</v>
+        <v>275</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>12</v>
@@ -4602,16 +5081,16 @@
     </row>
     <row r="65" spans="1:24" ht="13.75" customHeight="1">
       <c r="A65" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>138</v>
+        <v>276</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>12</v>
@@ -4640,16 +5119,16 @@
     </row>
     <row r="66" spans="1:24" ht="13.75" customHeight="1">
       <c r="A66" s="8" t="s">
-        <v>220</v>
+        <v>137</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>146</v>
+        <v>277</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="E66" s="8" t="s">
         <v>12</v>
@@ -4657,9 +5136,7 @@
       <c r="F66" s="9">
         <v>3.9</v>
       </c>
-      <c r="G66" s="8" t="s">
-        <v>13</v>
-      </c>
+      <c r="G66" s="12"/>
       <c r="H66" s="12"/>
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
@@ -4680,16 +5157,16 @@
     </row>
     <row r="67" spans="1:24" ht="13.75" customHeight="1">
       <c r="A67" s="8" t="s">
-        <v>147</v>
+        <v>203</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>148</v>
+        <v>278</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>12</v>
@@ -4698,7 +5175,7 @@
         <v>3.9</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>149</v>
+        <v>13</v>
       </c>
       <c r="H67" s="12"/>
       <c r="I67" s="5"/>
@@ -4720,16 +5197,16 @@
     </row>
     <row r="68" spans="1:24" ht="13.75" customHeight="1">
       <c r="A68" s="8" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>151</v>
+        <v>279</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>12</v>
@@ -4738,11 +5215,9 @@
         <v>3.9</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H68" s="8" t="s">
-        <v>48</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="H68" s="12"/>
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
@@ -4762,25 +5237,25 @@
     </row>
     <row r="69" spans="1:24" ht="13.75" customHeight="1">
       <c r="A69" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>153</v>
+        <v>280</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F69" s="9">
-        <v>4.9000000000000004</v>
+        <v>3.9</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>149</v>
+        <v>23</v>
       </c>
       <c r="H69" s="8" t="s">
         <v>48</v>
@@ -4803,14 +5278,30 @@
       <c r="X69" s="5"/>
     </row>
     <row r="70" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A70" s="5"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
+      <c r="A70" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" s="9">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
       <c r="K70" s="5"/>
@@ -27847,6 +28338,9 @@
       <c r="F956" s="5"/>
       <c r="G956" s="5"/>
       <c r="H956" s="5"/>
+      <c r="I956" s="5"/>
+      <c r="J956" s="5"/>
+      <c r="K956" s="5"/>
       <c r="L956" s="5"/>
       <c r="M956" s="5"/>
       <c r="N956" s="5"/>
@@ -27861,12 +28355,42 @@
       <c r="W956" s="5"/>
       <c r="X956" s="5"/>
     </row>
+    <row r="957" spans="1:24" ht="13.75" customHeight="1">
+      <c r="A957" s="5"/>
+      <c r="B957" s="6"/>
+      <c r="C957" s="6"/>
+      <c r="D957" s="5"/>
+      <c r="E957" s="5"/>
+      <c r="F957" s="5"/>
+      <c r="G957" s="5"/>
+      <c r="H957" s="5"/>
+      <c r="L957" s="5"/>
+      <c r="M957" s="5"/>
+      <c r="N957" s="5"/>
+      <c r="O957" s="5"/>
+      <c r="P957" s="5"/>
+      <c r="Q957" s="5"/>
+      <c r="R957" s="5"/>
+      <c r="S957" s="5"/>
+      <c r="T957" s="5"/>
+      <c r="U957" s="5"/>
+      <c r="V957" s="5"/>
+      <c r="W957" s="5"/>
+      <c r="X957" s="5"/>
+    </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1:K38" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"warm,cold"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <conditionalFormatting sqref="I2:L37">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>

--- a/data/CaterNow_Data_master.xlsx
+++ b/data/CaterNow_Data_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benedicthorbelt/Documents/Github/uni-caternow-booking-service/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA38C41F-D53E-C948-BD99-FBE34979B334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE3C7AF-FB2A-734C-A38D-24B4260D9B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="940" windowWidth="30020" windowHeight="19100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="160" yWindow="940" windowWidth="25180" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MainData" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Desserts" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MainData!$B$1:$P$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MainData!$B$1:$P$137</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="511">
   <si>
     <t>productTitle</t>
   </si>
@@ -1532,6 +1532,48 @@
   <si>
     <t>img_link</t>
   </si>
+  <si>
+    <t>Baklava</t>
+  </si>
+  <si>
+    <t>Knuspriges Blätterteiggebäck mit gehackten Pistazien und Walnüssen, großzügig getränkt in Rosenwasser-Honigsirup</t>
+  </si>
+  <si>
+    <t>Kunafa</t>
+  </si>
+  <si>
+    <t>Warmes Engelshaar-Gebäck gefüllt mit cremigem Frischkäse, übergossen mit Zuckersirup und garniert mit gemahlenen Pistazien</t>
+  </si>
+  <si>
+    <t>Muhallebi</t>
+  </si>
+  <si>
+    <t>Zarter Milchreis-Pudding parfümiert mit Rosenwasser und Orangenblüten, garniert mit gemahlenen Pistazien und getrockneten Rosenblättern</t>
+  </si>
+  <si>
+    <t>Halva mit Pistazien</t>
+  </si>
+  <si>
+    <t>Traditionelle Sesampaste-Konfekt mit gerösteten Pistazien und einem Hauch Kardamom, serviert mit frischen Feigen</t>
+  </si>
+  <si>
+    <t>Mango Sticky Rice</t>
+  </si>
+  <si>
+    <t>Klebreis mit frischer Alphonso-Mango und cremiger Kokosmilchsauce, verfeinert mit geröstetem Sesam</t>
+  </si>
+  <si>
+    <t>Matcha Panna Cotta</t>
+  </si>
+  <si>
+    <t>Seidige Panna Cotta mit hochwertigem japanischen Matcha, serviert mit einem Yuzu-Gelee und weißer Schokolade</t>
+  </si>
+  <si>
+    <t>Black Sesame Mochi</t>
+  </si>
+  <si>
+    <t>Zarte Reiskuchen gefüllt mit cremiger schwarzer Sesampaste und Azuki-Bohnencreme, leicht gepudert mit Stärke</t>
+  </si>
 </sst>
 </file>
 
@@ -2821,7 +2863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X930"/>
@@ -2953,7 +2995,7 @@
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
     </row>
-    <row r="3" spans="1:24" ht="13.75" customHeight="1">
+    <row r="3" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A3" s="31">
         <v>102</v>
       </c>
@@ -3001,7 +3043,7 @@
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
     </row>
-    <row r="4" spans="1:24" ht="13.75" customHeight="1">
+    <row r="4" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A4" s="31">
         <v>103</v>
       </c>
@@ -3055,7 +3097,7 @@
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
     </row>
-    <row r="5" spans="1:24" ht="13.75" customHeight="1">
+    <row r="5" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A5" s="31">
         <v>104</v>
       </c>
@@ -3109,7 +3151,7 @@
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
     </row>
-    <row r="6" spans="1:24" ht="13.75" customHeight="1">
+    <row r="6" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A6" s="31">
         <v>105</v>
       </c>
@@ -3163,7 +3205,7 @@
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
     </row>
-    <row r="7" spans="1:24" ht="13.75" customHeight="1">
+    <row r="7" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A7" s="31">
         <v>106</v>
       </c>
@@ -3217,7 +3259,7 @@
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
     </row>
-    <row r="8" spans="1:24" ht="13.75" customHeight="1">
+    <row r="8" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A8" s="31">
         <v>107</v>
       </c>
@@ -3271,7 +3313,7 @@
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
     </row>
-    <row r="9" spans="1:24" ht="13.75" customHeight="1">
+    <row r="9" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A9" s="31">
         <v>108</v>
       </c>
@@ -3323,7 +3365,7 @@
       <c r="W9" s="5"/>
       <c r="X9" s="5"/>
     </row>
-    <row r="10" spans="1:24" ht="13.75" customHeight="1">
+    <row r="10" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A10" s="31">
         <v>109</v>
       </c>
@@ -3377,7 +3419,7 @@
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
     </row>
-    <row r="11" spans="1:24" ht="13.75" customHeight="1">
+    <row r="11" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A11" s="31">
         <v>110</v>
       </c>
@@ -3427,7 +3469,7 @@
       <c r="W11" s="5"/>
       <c r="X11" s="5"/>
     </row>
-    <row r="12" spans="1:24" ht="13.75" customHeight="1">
+    <row r="12" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A12" s="31">
         <v>111</v>
       </c>
@@ -3477,7 +3519,7 @@
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
     </row>
-    <row r="13" spans="1:24" ht="13.75" customHeight="1">
+    <row r="13" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A13" s="31">
         <v>112</v>
       </c>
@@ -3527,7 +3569,7 @@
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
     </row>
-    <row r="14" spans="1:24" ht="13.75" customHeight="1">
+    <row r="14" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A14" s="31">
         <v>113</v>
       </c>
@@ -3579,7 +3621,7 @@
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
     </row>
-    <row r="15" spans="1:24" ht="13.75" customHeight="1">
+    <row r="15" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A15" s="31">
         <v>114</v>
       </c>
@@ -3629,7 +3671,7 @@
       <c r="W15" s="5"/>
       <c r="X15" s="5"/>
     </row>
-    <row r="16" spans="1:24" ht="13.75" customHeight="1">
+    <row r="16" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A16" s="31">
         <v>115</v>
       </c>
@@ -3679,7 +3721,7 @@
       <c r="W16" s="5"/>
       <c r="X16" s="5"/>
     </row>
-    <row r="17" spans="1:24" ht="13.75" customHeight="1">
+    <row r="17" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A17" s="31">
         <v>116</v>
       </c>
@@ -3731,7 +3773,7 @@
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
     </row>
-    <row r="18" spans="1:24" ht="13.75" customHeight="1">
+    <row r="18" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A18" s="31">
         <v>117</v>
       </c>
@@ -3785,7 +3827,7 @@
       <c r="W18" s="5"/>
       <c r="X18" s="5"/>
     </row>
-    <row r="19" spans="1:24" ht="13.75" customHeight="1">
+    <row r="19" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A19" s="31">
         <v>118</v>
       </c>
@@ -3839,7 +3881,7 @@
       <c r="W19" s="5"/>
       <c r="X19" s="5"/>
     </row>
-    <row r="20" spans="1:24" ht="13.75" customHeight="1">
+    <row r="20" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A20" s="31">
         <v>119</v>
       </c>
@@ -3891,7 +3933,7 @@
       <c r="W20" s="5"/>
       <c r="X20" s="5"/>
     </row>
-    <row r="21" spans="1:24" ht="13.75" customHeight="1">
+    <row r="21" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A21" s="31">
         <v>120</v>
       </c>
@@ -3945,7 +3987,7 @@
       <c r="W21" s="5"/>
       <c r="X21" s="5"/>
     </row>
-    <row r="22" spans="1:24" ht="13.75" customHeight="1">
+    <row r="22" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A22" s="31">
         <v>121</v>
       </c>
@@ -3999,7 +4041,7 @@
       <c r="W22" s="5"/>
       <c r="X22" s="5"/>
     </row>
-    <row r="23" spans="1:24" ht="13.75" customHeight="1">
+    <row r="23" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A23" s="31">
         <v>122</v>
       </c>
@@ -4051,7 +4093,7 @@
       <c r="W23" s="5"/>
       <c r="X23" s="5"/>
     </row>
-    <row r="24" spans="1:24" ht="13.75" customHeight="1">
+    <row r="24" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A24" s="31">
         <v>123</v>
       </c>
@@ -4105,7 +4147,7 @@
       <c r="W24" s="5"/>
       <c r="X24" s="5"/>
     </row>
-    <row r="25" spans="1:24" ht="13.75" customHeight="1">
+    <row r="25" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A25" s="31">
         <v>124</v>
       </c>
@@ -4159,7 +4201,7 @@
       <c r="W25" s="5"/>
       <c r="X25" s="5"/>
     </row>
-    <row r="26" spans="1:24" ht="13.75" customHeight="1">
+    <row r="26" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A26" s="31">
         <v>125</v>
       </c>
@@ -4213,7 +4255,7 @@
       <c r="W26" s="5"/>
       <c r="X26" s="5"/>
     </row>
-    <row r="27" spans="1:24" ht="13.75" customHeight="1">
+    <row r="27" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A27" s="31">
         <v>126</v>
       </c>
@@ -4267,7 +4309,7 @@
       <c r="W27" s="5"/>
       <c r="X27" s="5"/>
     </row>
-    <row r="28" spans="1:24" ht="13.75" customHeight="1">
+    <row r="28" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A28" s="31">
         <v>127</v>
       </c>
@@ -4321,7 +4363,7 @@
       <c r="W28" s="5"/>
       <c r="X28" s="5"/>
     </row>
-    <row r="29" spans="1:24" ht="13.75" customHeight="1">
+    <row r="29" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A29" s="31">
         <v>128</v>
       </c>
@@ -4375,7 +4417,7 @@
       <c r="W29" s="5"/>
       <c r="X29" s="5"/>
     </row>
-    <row r="30" spans="1:24" ht="13.75" customHeight="1">
+    <row r="30" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A30" s="31">
         <v>129</v>
       </c>
@@ -4610,7 +4652,9 @@
       <c r="H34" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I34" s="5"/>
+      <c r="I34" s="21" t="s">
+        <v>278</v>
+      </c>
       <c r="J34" s="24">
         <v>0.5</v>
       </c>
@@ -4662,7 +4706,9 @@
       <c r="H35" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I35" s="5"/>
+      <c r="I35" s="21" t="s">
+        <v>278</v>
+      </c>
       <c r="J35" s="24">
         <v>0.5</v>
       </c>
@@ -4793,7 +4839,7 @@
       <c r="W37" s="5"/>
       <c r="X37" s="5"/>
     </row>
-    <row r="38" spans="1:24" ht="13.75" customHeight="1">
+    <row r="38" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A38" s="31">
         <v>137</v>
       </c>
@@ -4845,7 +4891,7 @@
       <c r="W38" s="5"/>
       <c r="X38" s="5"/>
     </row>
-    <row r="39" spans="1:24" ht="13.75" customHeight="1">
+    <row r="39" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A39" s="31">
         <v>138</v>
       </c>
@@ -4897,7 +4943,7 @@
       <c r="W39" s="5"/>
       <c r="X39" s="5"/>
     </row>
-    <row r="40" spans="1:24" ht="13.75" customHeight="1">
+    <row r="40" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A40" s="31">
         <v>139</v>
       </c>
@@ -4951,7 +4997,7 @@
       <c r="W40" s="5"/>
       <c r="X40" s="5"/>
     </row>
-    <row r="41" spans="1:24" ht="13.75" customHeight="1">
+    <row r="41" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A41" s="31">
         <v>140</v>
       </c>
@@ -5003,7 +5049,7 @@
       <c r="W41" s="5"/>
       <c r="X41" s="5"/>
     </row>
-    <row r="42" spans="1:24" ht="13.75" customHeight="1">
+    <row r="42" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A42" s="31">
         <v>141</v>
       </c>
@@ -5053,7 +5099,7 @@
       <c r="W42" s="5"/>
       <c r="X42" s="5"/>
     </row>
-    <row r="43" spans="1:24" ht="13.75" customHeight="1">
+    <row r="43" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A43" s="31">
         <v>142</v>
       </c>
@@ -5105,7 +5151,7 @@
       <c r="W43" s="5"/>
       <c r="X43" s="5"/>
     </row>
-    <row r="44" spans="1:24" ht="13.75" customHeight="1">
+    <row r="44" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A44" s="31">
         <v>143</v>
       </c>
@@ -5155,7 +5201,7 @@
       <c r="W44" s="5"/>
       <c r="X44" s="5"/>
     </row>
-    <row r="45" spans="1:24" ht="13.75" customHeight="1">
+    <row r="45" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A45" s="31">
         <v>144</v>
       </c>
@@ -5363,7 +5409,7 @@
       <c r="W48" s="5"/>
       <c r="X48" s="5"/>
     </row>
-    <row r="49" spans="1:24" ht="13.75" customHeight="1">
+    <row r="49" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A49" s="31">
         <v>148</v>
       </c>
@@ -5415,7 +5461,7 @@
       <c r="W49" s="5"/>
       <c r="X49" s="5"/>
     </row>
-    <row r="50" spans="1:24" ht="13.75" customHeight="1">
+    <row r="50" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A50" s="31">
         <v>149</v>
       </c>
@@ -5467,7 +5513,7 @@
       <c r="W50" s="5"/>
       <c r="X50" s="5"/>
     </row>
-    <row r="51" spans="1:24" ht="13.75" customHeight="1">
+    <row r="51" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A51" s="31">
         <v>150</v>
       </c>
@@ -5519,7 +5565,7 @@
       <c r="W51" s="5"/>
       <c r="X51" s="5"/>
     </row>
-    <row r="52" spans="1:24" ht="13.75" customHeight="1">
+    <row r="52" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A52" s="31">
         <v>151</v>
       </c>
@@ -5571,7 +5617,7 @@
       <c r="W52" s="5"/>
       <c r="X52" s="5"/>
     </row>
-    <row r="53" spans="1:24" ht="15.75" customHeight="1">
+    <row r="53" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A53" s="31">
         <v>152</v>
       </c>
@@ -5613,7 +5659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:24" ht="15.75" customHeight="1">
+    <row r="54" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A54" s="31">
         <v>153</v>
       </c>
@@ -5655,7 +5701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:24" ht="15.75" customHeight="1">
+    <row r="55" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A55" s="31">
         <v>154</v>
       </c>
@@ -5695,7 +5741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:24" ht="15.75" customHeight="1">
+    <row r="56" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A56" s="31">
         <v>155</v>
       </c>
@@ -5737,7 +5783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:24" ht="15.75" customHeight="1">
+    <row r="57" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A57" s="31">
         <v>156</v>
       </c>
@@ -5779,7 +5825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:24" ht="15.75" customHeight="1">
+    <row r="58" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A58" s="31">
         <v>157</v>
       </c>
@@ -5821,7 +5867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:24" ht="15.75" customHeight="1">
+    <row r="59" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A59" s="31">
         <v>158</v>
       </c>
@@ -5949,7 +5995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:24" ht="15.75" customHeight="1">
+    <row r="62" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A62" s="31">
         <v>161</v>
       </c>
@@ -5991,7 +6037,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="63" spans="1:24" ht="15.75" customHeight="1">
+    <row r="63" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A63" s="31">
         <v>162</v>
       </c>
@@ -6031,7 +6077,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="64" spans="1:24" ht="15.75" customHeight="1">
+    <row r="64" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A64" s="31">
         <v>163</v>
       </c>
@@ -6073,7 +6119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:24" ht="13.75" customHeight="1">
+    <row r="65" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A65" s="31">
         <v>164</v>
       </c>
@@ -6125,7 +6171,7 @@
       <c r="W65" s="5"/>
       <c r="X65" s="5"/>
     </row>
-    <row r="66" spans="1:24" ht="13.75" customHeight="1">
+    <row r="66" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A66" s="31">
         <v>165</v>
       </c>
@@ -6177,7 +6223,7 @@
       <c r="W66" s="5"/>
       <c r="X66" s="5"/>
     </row>
-    <row r="67" spans="1:24" ht="13.75" customHeight="1">
+    <row r="67" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A67" s="31">
         <v>166</v>
       </c>
@@ -6229,7 +6275,7 @@
       <c r="W67" s="5"/>
       <c r="X67" s="5"/>
     </row>
-    <row r="68" spans="1:24" ht="13.75" customHeight="1">
+    <row r="68" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A68" s="31">
         <v>167</v>
       </c>
@@ -6281,7 +6327,7 @@
       <c r="W68" s="5"/>
       <c r="X68" s="5"/>
     </row>
-    <row r="69" spans="1:24" ht="13.75" customHeight="1">
+    <row r="69" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A69" s="31">
         <v>168</v>
       </c>
@@ -6333,7 +6379,7 @@
       <c r="W69" s="5"/>
       <c r="X69" s="5"/>
     </row>
-    <row r="70" spans="1:24" ht="13.75" customHeight="1">
+    <row r="70" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A70" s="31">
         <v>169</v>
       </c>
@@ -6385,7 +6431,7 @@
       <c r="W70" s="5"/>
       <c r="X70" s="5"/>
     </row>
-    <row r="71" spans="1:24" ht="13.75" customHeight="1">
+    <row r="71" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A71" s="31">
         <v>170</v>
       </c>
@@ -6437,7 +6483,7 @@
       <c r="W71" s="5"/>
       <c r="X71" s="5"/>
     </row>
-    <row r="72" spans="1:24" ht="13.75" customHeight="1">
+    <row r="72" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A72" s="31">
         <v>171</v>
       </c>
@@ -6489,7 +6535,7 @@
       <c r="W72" s="5"/>
       <c r="X72" s="5"/>
     </row>
-    <row r="73" spans="1:24" ht="13.75" customHeight="1">
+    <row r="73" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A73" s="31">
         <v>172</v>
       </c>
@@ -6541,7 +6587,7 @@
       <c r="W73" s="5"/>
       <c r="X73" s="5"/>
     </row>
-    <row r="74" spans="1:24" ht="13.75" customHeight="1">
+    <row r="74" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A74" s="31">
         <v>173</v>
       </c>
@@ -6593,7 +6639,7 @@
       <c r="W74" s="5"/>
       <c r="X74" s="5"/>
     </row>
-    <row r="75" spans="1:24" ht="13.75" customHeight="1">
+    <row r="75" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A75" s="31">
         <v>174</v>
       </c>
@@ -6645,7 +6691,7 @@
       <c r="W75" s="5"/>
       <c r="X75" s="5"/>
     </row>
-    <row r="76" spans="1:24" ht="13.75" customHeight="1">
+    <row r="76" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A76" s="31">
         <v>175</v>
       </c>
@@ -6697,7 +6743,7 @@
       <c r="W76" s="5"/>
       <c r="X76" s="5"/>
     </row>
-    <row r="77" spans="1:24" ht="13.75" customHeight="1">
+    <row r="77" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A77" s="31">
         <v>176</v>
       </c>
@@ -6749,7 +6795,7 @@
       <c r="W77" s="5"/>
       <c r="X77" s="5"/>
     </row>
-    <row r="78" spans="1:24" ht="13.75" customHeight="1">
+    <row r="78" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A78" s="31">
         <v>177</v>
       </c>
@@ -6801,7 +6847,7 @@
       <c r="W78" s="5"/>
       <c r="X78" s="5"/>
     </row>
-    <row r="79" spans="1:24" ht="13.75" customHeight="1">
+    <row r="79" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A79" s="31">
         <v>178</v>
       </c>
@@ -6853,7 +6899,7 @@
       <c r="W79" s="5"/>
       <c r="X79" s="5"/>
     </row>
-    <row r="80" spans="1:24" ht="13.75" customHeight="1">
+    <row r="80" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A80" s="31">
         <v>179</v>
       </c>
@@ -6907,7 +6953,7 @@
       <c r="W80" s="5"/>
       <c r="X80" s="5"/>
     </row>
-    <row r="81" spans="1:24" ht="13.75" customHeight="1">
+    <row r="81" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A81" s="31">
         <v>180</v>
       </c>
@@ -6961,7 +7007,7 @@
       <c r="W81" s="5"/>
       <c r="X81" s="5"/>
     </row>
-    <row r="82" spans="1:24" ht="13.75" customHeight="1">
+    <row r="82" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A82" s="31">
         <v>181</v>
       </c>
@@ -7013,7 +7059,7 @@
       <c r="W82" s="5"/>
       <c r="X82" s="5"/>
     </row>
-    <row r="83" spans="1:24" ht="13.75" customHeight="1">
+    <row r="83" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A83" s="31">
         <v>182</v>
       </c>
@@ -7065,7 +7111,7 @@
       <c r="W83" s="5"/>
       <c r="X83" s="5"/>
     </row>
-    <row r="84" spans="1:24" ht="13.75" customHeight="1">
+    <row r="84" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A84" s="31">
         <v>183</v>
       </c>
@@ -7117,7 +7163,7 @@
       <c r="W84" s="5"/>
       <c r="X84" s="5"/>
     </row>
-    <row r="85" spans="1:24" ht="13.75" customHeight="1">
+    <row r="85" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A85" s="31">
         <v>184</v>
       </c>
@@ -7169,7 +7215,7 @@
       <c r="W85" s="5"/>
       <c r="X85" s="5"/>
     </row>
-    <row r="86" spans="1:24" ht="13.75" customHeight="1">
+    <row r="86" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A86" s="31">
         <v>185</v>
       </c>
@@ -7219,7 +7265,7 @@
       <c r="W86" s="5"/>
       <c r="X86" s="5"/>
     </row>
-    <row r="87" spans="1:24" ht="13.75" customHeight="1">
+    <row r="87" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A87" s="31">
         <v>186</v>
       </c>
@@ -7269,7 +7315,7 @@
       <c r="W87" s="5"/>
       <c r="X87" s="5"/>
     </row>
-    <row r="88" spans="1:24" ht="13.75" customHeight="1">
+    <row r="88" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A88" s="31">
         <v>187</v>
       </c>
@@ -7321,7 +7367,7 @@
       <c r="W88" s="5"/>
       <c r="X88" s="5"/>
     </row>
-    <row r="89" spans="1:24" ht="13.75" customHeight="1">
+    <row r="89" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A89" s="31">
         <v>188</v>
       </c>
@@ -7373,7 +7419,7 @@
       <c r="W89" s="5"/>
       <c r="X89" s="5"/>
     </row>
-    <row r="90" spans="1:24" ht="13.75" customHeight="1">
+    <row r="90" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A90" s="31">
         <v>189</v>
       </c>
@@ -7425,7 +7471,7 @@
       <c r="W90" s="5"/>
       <c r="X90" s="5"/>
     </row>
-    <row r="91" spans="1:24" ht="13.75" customHeight="1">
+    <row r="91" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A91" s="31">
         <v>190</v>
       </c>
@@ -7477,7 +7523,7 @@
       <c r="W91" s="5"/>
       <c r="X91" s="5"/>
     </row>
-    <row r="92" spans="1:24" ht="13.75" customHeight="1">
+    <row r="92" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A92" s="31">
         <v>191</v>
       </c>
@@ -7529,7 +7575,7 @@
       <c r="W92" s="5"/>
       <c r="X92" s="5"/>
     </row>
-    <row r="93" spans="1:24" ht="13.75" customHeight="1">
+    <row r="93" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A93" s="31">
         <v>192</v>
       </c>
@@ -7581,7 +7627,7 @@
       <c r="W93" s="5"/>
       <c r="X93" s="5"/>
     </row>
-    <row r="94" spans="1:24" ht="13.75" customHeight="1">
+    <row r="94" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A94" s="31">
         <v>193</v>
       </c>
@@ -7633,7 +7679,7 @@
       <c r="W94" s="5"/>
       <c r="X94" s="5"/>
     </row>
-    <row r="95" spans="1:24" ht="13.75" customHeight="1">
+    <row r="95" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A95" s="31">
         <v>194</v>
       </c>
@@ -7683,7 +7729,7 @@
       <c r="W95" s="5"/>
       <c r="X95" s="5"/>
     </row>
-    <row r="96" spans="1:24" ht="13.75" customHeight="1">
+    <row r="96" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A96" s="31">
         <v>195</v>
       </c>
@@ -7735,7 +7781,7 @@
       <c r="W96" s="5"/>
       <c r="X96" s="5"/>
     </row>
-    <row r="97" spans="1:24" ht="13.75" customHeight="1">
+    <row r="97" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A97" s="31">
         <v>196</v>
       </c>
@@ -7787,7 +7833,7 @@
       <c r="W97" s="5"/>
       <c r="X97" s="5"/>
     </row>
-    <row r="98" spans="1:24" ht="13.75" customHeight="1">
+    <row r="98" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A98" s="31">
         <v>197</v>
       </c>
@@ -7839,7 +7885,7 @@
       <c r="W98" s="5"/>
       <c r="X98" s="5"/>
     </row>
-    <row r="99" spans="1:24" ht="13.75" customHeight="1">
+    <row r="99" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A99" s="31">
         <v>198</v>
       </c>
@@ -7891,7 +7937,7 @@
       <c r="W99" s="5"/>
       <c r="X99" s="5"/>
     </row>
-    <row r="100" spans="1:24" ht="13.75" customHeight="1">
+    <row r="100" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A100" s="31">
         <v>199</v>
       </c>
@@ -7943,7 +7989,7 @@
       <c r="W100" s="5"/>
       <c r="X100" s="5"/>
     </row>
-    <row r="101" spans="1:24" ht="13.75" customHeight="1">
+    <row r="101" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A101" s="31">
         <v>200</v>
       </c>
@@ -7995,7 +8041,7 @@
       <c r="W101" s="5"/>
       <c r="X101" s="5"/>
     </row>
-    <row r="102" spans="1:24" ht="13.75" customHeight="1">
+    <row r="102" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A102" s="31">
         <v>201</v>
       </c>
@@ -8047,7 +8093,7 @@
       <c r="W102" s="5"/>
       <c r="X102" s="5"/>
     </row>
-    <row r="103" spans="1:24" ht="13.75" customHeight="1">
+    <row r="103" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A103" s="31">
         <v>202</v>
       </c>
@@ -8099,7 +8145,7 @@
       <c r="W103" s="5"/>
       <c r="X103" s="5"/>
     </row>
-    <row r="104" spans="1:24" ht="13.75" customHeight="1">
+    <row r="104" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A104" s="31">
         <v>203</v>
       </c>
@@ -8151,7 +8197,7 @@
       <c r="W104" s="5"/>
       <c r="X104" s="5"/>
     </row>
-    <row r="105" spans="1:24" ht="13.75" customHeight="1">
+    <row r="105" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A105" s="31">
         <v>204</v>
       </c>
@@ -8201,7 +8247,7 @@
       <c r="W105" s="5"/>
       <c r="X105" s="5"/>
     </row>
-    <row r="106" spans="1:24" ht="13.75" customHeight="1">
+    <row r="106" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A106" s="31">
         <v>205</v>
       </c>
@@ -8251,7 +8297,7 @@
       <c r="W106" s="5"/>
       <c r="X106" s="5"/>
     </row>
-    <row r="107" spans="1:24" ht="13.75" customHeight="1">
+    <row r="107" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A107" s="31">
         <v>206</v>
       </c>
@@ -8303,7 +8349,7 @@
       <c r="W107" s="5"/>
       <c r="X107" s="5"/>
     </row>
-    <row r="108" spans="1:24" ht="13.75" customHeight="1">
+    <row r="108" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A108" s="31">
         <v>207</v>
       </c>
@@ -8355,7 +8401,7 @@
       <c r="W108" s="5"/>
       <c r="X108" s="5"/>
     </row>
-    <row r="109" spans="1:24" ht="13.75" customHeight="1">
+    <row r="109" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A109" s="31">
         <v>208</v>
       </c>
@@ -8407,7 +8453,7 @@
       <c r="W109" s="5"/>
       <c r="X109" s="5"/>
     </row>
-    <row r="110" spans="1:24" ht="13.75" customHeight="1">
+    <row r="110" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A110" s="31">
         <v>209</v>
       </c>
@@ -8459,7 +8505,7 @@
       <c r="W110" s="5"/>
       <c r="X110" s="5"/>
     </row>
-    <row r="111" spans="1:24" ht="13.75" customHeight="1">
+    <row r="111" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A111" s="31">
         <v>210</v>
       </c>
@@ -8511,7 +8557,7 @@
       <c r="W111" s="5"/>
       <c r="X111" s="5"/>
     </row>
-    <row r="112" spans="1:24" ht="13.75" customHeight="1">
+    <row r="112" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A112" s="31">
         <v>211</v>
       </c>
@@ -8563,7 +8609,7 @@
       <c r="W112" s="5"/>
       <c r="X112" s="5"/>
     </row>
-    <row r="113" spans="1:24" ht="13.75" customHeight="1">
+    <row r="113" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A113" s="31">
         <v>212</v>
       </c>
@@ -8615,7 +8661,7 @@
       <c r="W113" s="5"/>
       <c r="X113" s="5"/>
     </row>
-    <row r="114" spans="1:24" ht="13.75" customHeight="1">
+    <row r="114" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A114" s="31">
         <v>213</v>
       </c>
@@ -8667,7 +8713,7 @@
       <c r="W114" s="5"/>
       <c r="X114" s="5"/>
     </row>
-    <row r="115" spans="1:24" ht="13.75" customHeight="1">
+    <row r="115" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A115" s="31">
         <v>214</v>
       </c>
@@ -8719,7 +8765,7 @@
       <c r="W115" s="5"/>
       <c r="X115" s="5"/>
     </row>
-    <row r="116" spans="1:24" ht="13.75" customHeight="1">
+    <row r="116" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A116" s="31">
         <v>215</v>
       </c>
@@ -8771,7 +8817,7 @@
       <c r="W116" s="5"/>
       <c r="X116" s="5"/>
     </row>
-    <row r="117" spans="1:24" ht="13.75" customHeight="1">
+    <row r="117" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A117" s="31">
         <v>216</v>
       </c>
@@ -8823,7 +8869,7 @@
       <c r="W117" s="5"/>
       <c r="X117" s="5"/>
     </row>
-    <row r="118" spans="1:24" ht="13.75" customHeight="1">
+    <row r="118" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A118" s="31">
         <v>217</v>
       </c>
@@ -8875,7 +8921,7 @@
       <c r="W118" s="5"/>
       <c r="X118" s="5"/>
     </row>
-    <row r="119" spans="1:24" ht="13.75" customHeight="1">
+    <row r="119" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A119" s="31">
         <v>218</v>
       </c>
@@ -8925,7 +8971,7 @@
       <c r="W119" s="5"/>
       <c r="X119" s="5"/>
     </row>
-    <row r="120" spans="1:24" ht="13.75" customHeight="1">
+    <row r="120" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A120" s="31">
         <v>219</v>
       </c>
@@ -8975,7 +9021,7 @@
       <c r="W120" s="5"/>
       <c r="X120" s="5"/>
     </row>
-    <row r="121" spans="1:24" ht="13.75" customHeight="1">
+    <row r="121" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A121" s="31">
         <v>220</v>
       </c>
@@ -9025,7 +9071,7 @@
       <c r="W121" s="5"/>
       <c r="X121" s="5"/>
     </row>
-    <row r="122" spans="1:24" ht="13.75" customHeight="1">
+    <row r="122" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A122" s="31">
         <v>221</v>
       </c>
@@ -9075,7 +9121,7 @@
       <c r="W122" s="5"/>
       <c r="X122" s="5"/>
     </row>
-    <row r="123" spans="1:24" ht="13.75" customHeight="1">
+    <row r="123" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A123" s="31">
         <v>222</v>
       </c>
@@ -9127,7 +9173,7 @@
       <c r="W123" s="5"/>
       <c r="X123" s="5"/>
     </row>
-    <row r="124" spans="1:24" ht="13.75" customHeight="1">
+    <row r="124" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A124" s="31">
         <v>223</v>
       </c>
@@ -9179,7 +9225,7 @@
       <c r="W124" s="5"/>
       <c r="X124" s="5"/>
     </row>
-    <row r="125" spans="1:24" ht="13.75" customHeight="1">
+    <row r="125" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A125" s="31">
         <v>224</v>
       </c>
@@ -9231,7 +9277,7 @@
       <c r="W125" s="5"/>
       <c r="X125" s="5"/>
     </row>
-    <row r="126" spans="1:24" ht="13.75" customHeight="1">
+    <row r="126" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A126" s="31">
         <v>225</v>
       </c>
@@ -9281,7 +9327,7 @@
       <c r="W126" s="5"/>
       <c r="X126" s="5"/>
     </row>
-    <row r="127" spans="1:24" ht="13.75" customHeight="1">
+    <row r="127" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A127" s="31">
         <v>226</v>
       </c>
@@ -9331,7 +9377,7 @@
       <c r="W127" s="5"/>
       <c r="X127" s="5"/>
     </row>
-    <row r="128" spans="1:24" ht="13.75" customHeight="1">
+    <row r="128" spans="1:24" ht="13.75" hidden="1" customHeight="1">
       <c r="A128" s="31">
         <v>227</v>
       </c>
@@ -9385,19 +9431,45 @@
     </row>
     <row r="129" spans="1:24" ht="13.75" customHeight="1">
       <c r="A129" s="9"/>
-      <c r="B129" s="8"/>
-      <c r="C129" s="8"/>
-      <c r="D129" s="8"/>
-      <c r="E129" s="8"/>
-      <c r="F129" s="8"/>
-      <c r="G129" s="8"/>
-      <c r="H129" s="8"/>
-      <c r="I129" s="8"/>
-      <c r="J129" s="5"/>
-      <c r="K129" s="5"/>
-      <c r="L129" s="5"/>
-      <c r="M129" s="5"/>
-      <c r="N129" s="5"/>
+      <c r="B129" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F129" s="9">
+        <v>3.9</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H129" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I129" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="J129" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="K129" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="L129" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M129" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="N129" s="5">
+        <v>0</v>
+      </c>
       <c r="O129" s="5"/>
       <c r="P129" s="5"/>
       <c r="Q129" s="5"/>
@@ -9411,19 +9483,45 @@
     </row>
     <row r="130" spans="1:24" ht="13.75" customHeight="1">
       <c r="A130" s="9"/>
-      <c r="B130" s="8"/>
-      <c r="C130" s="8"/>
-      <c r="D130" s="8"/>
-      <c r="E130" s="8"/>
-      <c r="F130" s="8"/>
-      <c r="G130" s="8"/>
-      <c r="H130" s="8"/>
-      <c r="I130" s="8"/>
-      <c r="J130" s="5"/>
-      <c r="K130" s="5"/>
-      <c r="L130" s="5"/>
-      <c r="M130" s="5"/>
-      <c r="N130" s="5"/>
+      <c r="B130" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F130" s="9">
+        <v>3.9</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H130" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="J130" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="K130" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="L130" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M130" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="N130" s="5">
+        <v>0</v>
+      </c>
       <c r="O130" s="5"/>
       <c r="P130" s="5"/>
       <c r="Q130" s="5"/>
@@ -9437,19 +9535,43 @@
     </row>
     <row r="131" spans="1:24" ht="13.75" customHeight="1">
       <c r="A131" s="9"/>
-      <c r="B131" s="8"/>
-      <c r="C131" s="8"/>
-      <c r="D131" s="8"/>
-      <c r="E131" s="8"/>
-      <c r="F131" s="8"/>
-      <c r="G131" s="8"/>
-      <c r="H131" s="8"/>
-      <c r="I131" s="8"/>
-      <c r="J131" s="5"/>
-      <c r="K131" s="5"/>
-      <c r="L131" s="5"/>
-      <c r="M131" s="5"/>
-      <c r="N131" s="5"/>
+      <c r="B131" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F131" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H131" s="12"/>
+      <c r="I131" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="J131" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="K131" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="L131" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="M131" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="N131" s="5">
+        <v>0</v>
+      </c>
       <c r="O131" s="5"/>
       <c r="P131" s="5"/>
       <c r="Q131" s="5"/>
@@ -9463,19 +9585,45 @@
     </row>
     <row r="132" spans="1:24" ht="13.75" customHeight="1">
       <c r="A132" s="9"/>
-      <c r="B132" s="8"/>
-      <c r="C132" s="8"/>
-      <c r="D132" s="8"/>
-      <c r="E132" s="8"/>
-      <c r="F132" s="8"/>
-      <c r="G132" s="8"/>
-      <c r="H132" s="8"/>
-      <c r="I132" s="8"/>
-      <c r="J132" s="5"/>
-      <c r="K132" s="5"/>
-      <c r="L132" s="5"/>
-      <c r="M132" s="5"/>
-      <c r="N132" s="5"/>
+      <c r="B132" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F132" s="9">
+        <v>3.9</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H132" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I132" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="J132" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="K132" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="L132" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="M132" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="N132" s="5">
+        <v>0</v>
+      </c>
       <c r="O132" s="5"/>
       <c r="P132" s="5"/>
       <c r="Q132" s="5"/>
@@ -9489,19 +9637,43 @@
     </row>
     <row r="133" spans="1:24" ht="13.75" customHeight="1">
       <c r="A133" s="9"/>
-      <c r="B133" s="8"/>
-      <c r="C133" s="8"/>
-      <c r="D133" s="8"/>
-      <c r="E133" s="8"/>
-      <c r="F133" s="8"/>
-      <c r="G133" s="8"/>
-      <c r="H133" s="8"/>
-      <c r="I133" s="8"/>
-      <c r="J133" s="5"/>
-      <c r="K133" s="5"/>
-      <c r="L133" s="5"/>
-      <c r="M133" s="5"/>
-      <c r="N133" s="5"/>
+      <c r="B133" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C133" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F133" s="9">
+        <v>3.9</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H133" s="12"/>
+      <c r="I133" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="J133" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="K133" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="L133" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="M133" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="N133" s="5">
+        <v>0</v>
+      </c>
       <c r="O133" s="5"/>
       <c r="P133" s="5"/>
       <c r="Q133" s="5"/>
@@ -9515,19 +9687,45 @@
     </row>
     <row r="134" spans="1:24" ht="13.75" customHeight="1">
       <c r="A134" s="9"/>
-      <c r="B134" s="8"/>
-      <c r="C134" s="8"/>
-      <c r="D134" s="8"/>
-      <c r="E134" s="8"/>
-      <c r="F134" s="8"/>
-      <c r="G134" s="8"/>
-      <c r="H134" s="8"/>
-      <c r="I134" s="8"/>
-      <c r="J134" s="5"/>
-      <c r="K134" s="5"/>
-      <c r="L134" s="5"/>
-      <c r="M134" s="5"/>
-      <c r="N134" s="5"/>
+      <c r="B134" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C134" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F134" s="9">
+        <v>3.9</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H134" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I134" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="J134" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="K134" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="L134" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="M134" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="N134" s="5">
+        <v>0</v>
+      </c>
       <c r="O134" s="5"/>
       <c r="P134" s="5"/>
       <c r="Q134" s="5"/>
@@ -9541,19 +9739,45 @@
     </row>
     <row r="135" spans="1:24" ht="13.75" customHeight="1">
       <c r="A135" s="9"/>
-      <c r="B135" s="8"/>
-      <c r="C135" s="8"/>
-      <c r="D135" s="8"/>
-      <c r="E135" s="8"/>
-      <c r="F135" s="8"/>
-      <c r="G135" s="8"/>
-      <c r="H135" s="8"/>
-      <c r="I135" s="8"/>
-      <c r="J135" s="5"/>
-      <c r="K135" s="5"/>
-      <c r="L135" s="5"/>
-      <c r="M135" s="5"/>
-      <c r="N135" s="5"/>
+      <c r="B135" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F135" s="9">
+        <v>3.9</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H135" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I135" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="J135" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="K135" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="L135" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="M135" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="N135" s="5">
+        <v>0</v>
+      </c>
       <c r="O135" s="5"/>
       <c r="P135" s="5"/>
       <c r="Q135" s="5"/>
@@ -9567,11 +9791,43 @@
     </row>
     <row r="136" spans="1:24" ht="13.75" customHeight="1">
       <c r="A136" s="9"/>
-      <c r="J136" s="5"/>
-      <c r="K136" s="5"/>
-      <c r="L136" s="5"/>
-      <c r="M136" s="5"/>
-      <c r="N136" s="5"/>
+      <c r="B136" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F136" s="9">
+        <v>2.5</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H136" s="12"/>
+      <c r="I136" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="J136" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="K136" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="L136" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="M136" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="N136" s="5">
+        <v>0</v>
+      </c>
       <c r="O136" s="5"/>
       <c r="P136" s="5"/>
       <c r="Q136" s="5"/>
@@ -9584,12 +9840,44 @@
       <c r="X136" s="5"/>
     </row>
     <row r="137" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A137" s="9"/>
-      <c r="J137" s="5"/>
-      <c r="K137" s="5"/>
-      <c r="L137" s="5"/>
-      <c r="M137" s="5"/>
-      <c r="N137" s="5"/>
+      <c r="A137"/>
+      <c r="B137" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F137" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="H137" s="8"/>
+      <c r="I137" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="J137" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="K137" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="L137" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="M137" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="N137" s="5">
+        <v>0</v>
+      </c>
       <c r="O137" s="5"/>
       <c r="P137" s="5"/>
       <c r="Q137" s="5"/>
@@ -9603,11 +9891,45 @@
     </row>
     <row r="138" spans="1:24" ht="13.75" customHeight="1">
       <c r="A138" s="9"/>
-      <c r="J138" s="5"/>
-      <c r="K138" s="5"/>
-      <c r="L138" s="5"/>
-      <c r="M138" s="5"/>
-      <c r="N138" s="5"/>
+      <c r="B138" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F138" s="9">
+        <v>3.9</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="H138" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="J138" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="K138" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="L138" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M138" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="N138" s="5">
+        <v>0</v>
+      </c>
       <c r="O138" s="5"/>
       <c r="P138" s="5"/>
       <c r="Q138" s="5"/>
@@ -9621,11 +9943,45 @@
     </row>
     <row r="139" spans="1:24" ht="13.75" customHeight="1">
       <c r="A139" s="9"/>
-      <c r="J139" s="5"/>
-      <c r="K139" s="5"/>
-      <c r="L139" s="5"/>
-      <c r="M139" s="5"/>
-      <c r="N139" s="5"/>
+      <c r="B139" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F139" s="9">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H139" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I139" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="J139" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="K139" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="L139" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="M139" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="N139" s="5">
+        <v>0</v>
+      </c>
       <c r="O139" s="5"/>
       <c r="P139" s="5"/>
       <c r="Q139" s="5"/>
@@ -9639,11 +9995,43 @@
     </row>
     <row r="140" spans="1:24" ht="13.75" customHeight="1">
       <c r="A140" s="9"/>
-      <c r="J140" s="5"/>
-      <c r="K140" s="5"/>
-      <c r="L140" s="5"/>
-      <c r="M140" s="5"/>
-      <c r="N140" s="5"/>
+      <c r="B140" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F140" s="9">
+        <v>3.9</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H140" s="8"/>
+      <c r="I140" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="J140" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="K140" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="L140" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="M140" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="N140" s="5">
+        <v>0</v>
+      </c>
       <c r="O140" s="5"/>
       <c r="P140" s="5"/>
       <c r="Q140" s="5"/>
@@ -9657,11 +10045,43 @@
     </row>
     <row r="141" spans="1:24" ht="13.75" customHeight="1">
       <c r="A141" s="9"/>
-      <c r="J141" s="5"/>
-      <c r="K141" s="5"/>
-      <c r="L141" s="5"/>
-      <c r="M141" s="5"/>
-      <c r="N141" s="5"/>
+      <c r="B141" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F141" s="9">
+        <v>3.9</v>
+      </c>
+      <c r="G141" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="H141" s="8"/>
+      <c r="I141" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="J141" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="K141" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="L141" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="M141" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="N141" s="5">
+        <v>0</v>
+      </c>
       <c r="O141" s="5"/>
       <c r="P141" s="5"/>
       <c r="Q141" s="5"/>
@@ -9675,11 +10095,41 @@
     </row>
     <row r="142" spans="1:24" ht="13.75" customHeight="1">
       <c r="A142" s="9"/>
-      <c r="J142" s="5"/>
-      <c r="K142" s="5"/>
-      <c r="L142" s="5"/>
-      <c r="M142" s="5"/>
-      <c r="N142" s="5"/>
+      <c r="B142" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F142" s="9">
+        <v>3.9</v>
+      </c>
+      <c r="G142" s="8"/>
+      <c r="H142" s="8"/>
+      <c r="I142" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="J142" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="K142" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="L142" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M142" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="N142" s="5">
+        <v>0</v>
+      </c>
       <c r="O142" s="5"/>
       <c r="P142" s="5"/>
       <c r="Q142" s="5"/>
@@ -9693,11 +10143,43 @@
     </row>
     <row r="143" spans="1:24" ht="13.75" customHeight="1">
       <c r="A143" s="9"/>
-      <c r="J143" s="5"/>
-      <c r="K143" s="5"/>
-      <c r="L143" s="5"/>
-      <c r="M143" s="5"/>
-      <c r="N143" s="5"/>
+      <c r="B143" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F143" s="9">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H143" s="8"/>
+      <c r="I143" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="J143" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="K143" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="L143" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="M143" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="N143" s="5">
+        <v>0</v>
+      </c>
       <c r="O143" s="5"/>
       <c r="P143" s="5"/>
       <c r="Q143" s="5"/>
@@ -9711,11 +10193,41 @@
     </row>
     <row r="144" spans="1:24" ht="13.75" customHeight="1">
       <c r="A144" s="9"/>
-      <c r="J144" s="5"/>
-      <c r="K144" s="5"/>
-      <c r="L144" s="5"/>
-      <c r="M144" s="5"/>
-      <c r="N144" s="5"/>
+      <c r="B144" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E144" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F144" s="9">
+        <v>3.9</v>
+      </c>
+      <c r="G144" s="8"/>
+      <c r="H144" s="8"/>
+      <c r="I144" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="J144" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="K144" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="L144" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="M144" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="N144" s="5">
+        <v>0</v>
+      </c>
       <c r="O144" s="5"/>
       <c r="P144" s="5"/>
       <c r="Q144" s="5"/>
@@ -9729,6 +10241,13 @@
     </row>
     <row r="145" spans="1:24" ht="13.75" customHeight="1">
       <c r="A145" s="9"/>
+      <c r="B145" s="8"/>
+      <c r="C145" s="8"/>
+      <c r="D145" s="8"/>
+      <c r="E145" s="8"/>
+      <c r="F145" s="9"/>
+      <c r="G145" s="8"/>
+      <c r="H145" s="8"/>
       <c r="J145" s="5"/>
       <c r="K145" s="5"/>
       <c r="L145" s="5"/>
@@ -9747,6 +10266,13 @@
     </row>
     <row r="146" spans="1:24" ht="13.75" customHeight="1">
       <c r="A146" s="9"/>
+      <c r="B146" s="8"/>
+      <c r="C146" s="8"/>
+      <c r="D146" s="8"/>
+      <c r="E146" s="8"/>
+      <c r="F146" s="9"/>
+      <c r="G146" s="8"/>
+      <c r="H146" s="8"/>
       <c r="J146" s="5"/>
       <c r="K146" s="5"/>
       <c r="L146" s="5"/>
@@ -9765,6 +10291,14 @@
     </row>
     <row r="147" spans="1:24" ht="13.75" customHeight="1">
       <c r="A147" s="9"/>
+      <c r="B147" s="8"/>
+      <c r="C147" s="8"/>
+      <c r="D147" s="8"/>
+      <c r="E147" s="8"/>
+      <c r="F147" s="9"/>
+      <c r="G147" s="8"/>
+      <c r="H147" s="8"/>
+      <c r="I147" s="8"/>
       <c r="J147" s="5"/>
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
@@ -9783,6 +10317,14 @@
     </row>
     <row r="148" spans="1:24" ht="13.75" customHeight="1">
       <c r="A148" s="9"/>
+      <c r="B148" s="8"/>
+      <c r="C148" s="8"/>
+      <c r="D148" s="8"/>
+      <c r="E148" s="8"/>
+      <c r="F148" s="9"/>
+      <c r="G148" s="8"/>
+      <c r="H148" s="8"/>
+      <c r="I148" s="8"/>
       <c r="J148" s="5"/>
       <c r="K148" s="5"/>
       <c r="L148" s="5"/>
@@ -9801,6 +10343,14 @@
     </row>
     <row r="149" spans="1:24" ht="13.75" customHeight="1">
       <c r="A149" s="9"/>
+      <c r="B149" s="8"/>
+      <c r="C149" s="8"/>
+      <c r="D149" s="8"/>
+      <c r="E149" s="8"/>
+      <c r="F149" s="9"/>
+      <c r="G149" s="8"/>
+      <c r="H149" s="8"/>
+      <c r="I149" s="8"/>
       <c r="J149" s="5"/>
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
@@ -9819,6 +10369,14 @@
     </row>
     <row r="150" spans="1:24" ht="13.75" customHeight="1">
       <c r="A150" s="9"/>
+      <c r="B150" s="8"/>
+      <c r="C150" s="8"/>
+      <c r="D150" s="8"/>
+      <c r="E150" s="8"/>
+      <c r="F150" s="9"/>
+      <c r="G150" s="8"/>
+      <c r="H150" s="8"/>
+      <c r="I150" s="8"/>
       <c r="J150" s="5"/>
       <c r="K150" s="5"/>
       <c r="L150" s="5"/>
@@ -9837,6 +10395,14 @@
     </row>
     <row r="151" spans="1:24" ht="13.75" customHeight="1">
       <c r="A151" s="9"/>
+      <c r="B151" s="8"/>
+      <c r="C151" s="8"/>
+      <c r="D151" s="8"/>
+      <c r="E151" s="8"/>
+      <c r="F151" s="9"/>
+      <c r="G151" s="8"/>
+      <c r="H151" s="8"/>
+      <c r="I151" s="8"/>
       <c r="J151" s="5"/>
       <c r="K151" s="5"/>
       <c r="L151" s="5"/>
@@ -9855,6 +10421,14 @@
     </row>
     <row r="152" spans="1:24" ht="13.75" customHeight="1">
       <c r="A152" s="9"/>
+      <c r="B152" s="8"/>
+      <c r="C152" s="8"/>
+      <c r="D152" s="8"/>
+      <c r="E152" s="8"/>
+      <c r="F152" s="9"/>
+      <c r="G152" s="8"/>
+      <c r="H152" s="8"/>
+      <c r="I152" s="8"/>
       <c r="J152" s="5"/>
       <c r="K152" s="5"/>
       <c r="L152" s="5"/>
@@ -9873,6 +10447,13 @@
     </row>
     <row r="153" spans="1:24" ht="13.75" customHeight="1">
       <c r="A153" s="9"/>
+      <c r="B153" s="8"/>
+      <c r="C153" s="8"/>
+      <c r="D153" s="8"/>
+      <c r="E153" s="8"/>
+      <c r="F153" s="9"/>
+      <c r="G153" s="8"/>
+      <c r="H153" s="8"/>
       <c r="J153" s="5"/>
       <c r="K153" s="5"/>
       <c r="L153" s="5"/>
@@ -9891,6 +10472,14 @@
     </row>
     <row r="154" spans="1:24" ht="13.75" customHeight="1">
       <c r="A154" s="9"/>
+      <c r="B154" s="8"/>
+      <c r="C154" s="8"/>
+      <c r="D154" s="8"/>
+      <c r="E154" s="8"/>
+      <c r="F154" s="9"/>
+      <c r="G154" s="8"/>
+      <c r="H154" s="8"/>
+      <c r="I154" s="8"/>
       <c r="J154" s="5"/>
       <c r="K154" s="5"/>
       <c r="L154" s="5"/>
@@ -9909,6 +10498,14 @@
     </row>
     <row r="155" spans="1:24" ht="13.75" customHeight="1">
       <c r="A155" s="9"/>
+      <c r="B155" s="8"/>
+      <c r="C155" s="8"/>
+      <c r="D155" s="8"/>
+      <c r="E155" s="8"/>
+      <c r="F155" s="9"/>
+      <c r="G155" s="8"/>
+      <c r="H155" s="8"/>
+      <c r="I155" s="8"/>
       <c r="J155" s="5"/>
       <c r="K155" s="5"/>
       <c r="L155" s="5"/>
@@ -9927,6 +10524,14 @@
     </row>
     <row r="156" spans="1:24" ht="13.75" customHeight="1">
       <c r="A156" s="9"/>
+      <c r="B156" s="8"/>
+      <c r="C156" s="8"/>
+      <c r="D156" s="8"/>
+      <c r="E156" s="8"/>
+      <c r="F156" s="9"/>
+      <c r="G156" s="8"/>
+      <c r="H156" s="8"/>
+      <c r="I156" s="8"/>
       <c r="J156" s="5"/>
       <c r="K156" s="5"/>
       <c r="L156" s="5"/>
@@ -9945,6 +10550,14 @@
     </row>
     <row r="157" spans="1:24" ht="13.75" customHeight="1">
       <c r="A157" s="9"/>
+      <c r="B157" s="8"/>
+      <c r="C157" s="8"/>
+      <c r="D157" s="8"/>
+      <c r="E157" s="8"/>
+      <c r="F157" s="9"/>
+      <c r="G157" s="8"/>
+      <c r="H157" s="8"/>
+      <c r="I157" s="8"/>
       <c r="J157" s="5"/>
       <c r="K157" s="5"/>
       <c r="L157" s="5"/>
@@ -9963,6 +10576,14 @@
     </row>
     <row r="158" spans="1:24" ht="13.75" customHeight="1">
       <c r="A158" s="9"/>
+      <c r="B158" s="8"/>
+      <c r="C158" s="8"/>
+      <c r="D158" s="8"/>
+      <c r="E158" s="8"/>
+      <c r="F158" s="9"/>
+      <c r="G158" s="8"/>
+      <c r="H158" s="8"/>
+      <c r="I158" s="8"/>
       <c r="J158" s="5"/>
       <c r="K158" s="5"/>
       <c r="L158" s="5"/>
@@ -9981,6 +10602,14 @@
     </row>
     <row r="159" spans="1:24" ht="13.75" customHeight="1">
       <c r="A159" s="9"/>
+      <c r="B159" s="8"/>
+      <c r="C159" s="8"/>
+      <c r="D159" s="8"/>
+      <c r="E159" s="8"/>
+      <c r="F159" s="9"/>
+      <c r="G159" s="8"/>
+      <c r="H159" s="8"/>
+      <c r="I159" s="8"/>
       <c r="J159" s="5"/>
       <c r="K159" s="5"/>
       <c r="L159" s="5"/>
@@ -9999,6 +10628,13 @@
     </row>
     <row r="160" spans="1:24" ht="13.75" customHeight="1">
       <c r="A160" s="9"/>
+      <c r="B160" s="8"/>
+      <c r="C160" s="8"/>
+      <c r="D160" s="8"/>
+      <c r="E160" s="8"/>
+      <c r="F160" s="9"/>
+      <c r="G160" s="8"/>
+      <c r="H160" s="8"/>
       <c r="J160" s="5"/>
       <c r="K160" s="5"/>
       <c r="L160" s="5"/>
@@ -10017,6 +10653,14 @@
     </row>
     <row r="161" spans="1:24" ht="13.75" customHeight="1">
       <c r="A161" s="9"/>
+      <c r="B161" s="8"/>
+      <c r="C161" s="8"/>
+      <c r="D161" s="8"/>
+      <c r="E161" s="8"/>
+      <c r="F161" s="9"/>
+      <c r="G161" s="8"/>
+      <c r="H161" s="8"/>
+      <c r="I161" s="8"/>
       <c r="J161" s="5"/>
       <c r="K161" s="5"/>
       <c r="L161" s="5"/>
@@ -10035,6 +10679,14 @@
     </row>
     <row r="162" spans="1:24" ht="13.75" customHeight="1">
       <c r="A162" s="9"/>
+      <c r="B162" s="8"/>
+      <c r="C162" s="8"/>
+      <c r="D162" s="8"/>
+      <c r="E162" s="8"/>
+      <c r="F162" s="9"/>
+      <c r="G162" s="8"/>
+      <c r="H162" s="8"/>
+      <c r="I162" s="8"/>
       <c r="J162" s="5"/>
       <c r="K162" s="5"/>
       <c r="L162" s="5"/>
@@ -10053,6 +10705,14 @@
     </row>
     <row r="163" spans="1:24" ht="13.75" customHeight="1">
       <c r="A163" s="9"/>
+      <c r="B163" s="8"/>
+      <c r="C163" s="8"/>
+      <c r="D163" s="8"/>
+      <c r="E163" s="8"/>
+      <c r="F163" s="9"/>
+      <c r="G163" s="8"/>
+      <c r="H163" s="8"/>
+      <c r="I163" s="8"/>
       <c r="J163" s="5"/>
       <c r="K163" s="5"/>
       <c r="L163" s="5"/>
@@ -10071,6 +10731,14 @@
     </row>
     <row r="164" spans="1:24" ht="13.75" customHeight="1">
       <c r="A164" s="9"/>
+      <c r="B164" s="8"/>
+      <c r="C164" s="8"/>
+      <c r="D164" s="8"/>
+      <c r="E164" s="8"/>
+      <c r="F164" s="9"/>
+      <c r="G164" s="8"/>
+      <c r="H164" s="8"/>
+      <c r="I164" s="8"/>
       <c r="J164" s="5"/>
       <c r="K164" s="5"/>
       <c r="L164" s="5"/>
@@ -10089,6 +10757,14 @@
     </row>
     <row r="165" spans="1:24" ht="13.75" customHeight="1">
       <c r="A165" s="9"/>
+      <c r="B165" s="8"/>
+      <c r="C165" s="8"/>
+      <c r="D165" s="8"/>
+      <c r="E165" s="8"/>
+      <c r="F165" s="9"/>
+      <c r="G165" s="8"/>
+      <c r="H165" s="8"/>
+      <c r="I165" s="8"/>
       <c r="J165" s="5"/>
       <c r="K165" s="5"/>
       <c r="L165" s="5"/>
@@ -10107,6 +10783,14 @@
     </row>
     <row r="166" spans="1:24" ht="13.75" customHeight="1">
       <c r="A166" s="9"/>
+      <c r="B166" s="8"/>
+      <c r="C166" s="8"/>
+      <c r="D166" s="8"/>
+      <c r="E166" s="8"/>
+      <c r="F166" s="9"/>
+      <c r="G166" s="8"/>
+      <c r="H166" s="8"/>
+      <c r="I166" s="8"/>
       <c r="J166" s="5"/>
       <c r="K166" s="5"/>
       <c r="L166" s="5"/>
@@ -10125,6 +10809,13 @@
     </row>
     <row r="167" spans="1:24" ht="13.75" customHeight="1">
       <c r="A167" s="9"/>
+      <c r="B167" s="8"/>
+      <c r="C167" s="8"/>
+      <c r="D167" s="8"/>
+      <c r="E167" s="8"/>
+      <c r="F167" s="9"/>
+      <c r="G167" s="8"/>
+      <c r="H167" s="8"/>
       <c r="J167" s="5"/>
       <c r="K167" s="5"/>
       <c r="L167" s="5"/>
@@ -29977,8 +30668,14 @@
       <c r="X930" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:P128" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="J2:N128">
+  <autoFilter ref="B1:P137" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Dessert"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="J2:N144">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -30002,6 +30699,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21CFA1F-1FDA-B147-8AC7-55852FE3510B}">
   <dimension ref="B2:I33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
+  <cols>
+    <col min="2" max="2" width="27.83203125" customWidth="1"/>
+    <col min="3" max="3" width="39.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="16">
       <c r="B2" s="8" t="s">
@@ -30051,32 +30752,6 @@
       </c>
       <c r="I3" s="21"/>
     </row>
-    <row r="4" spans="2:9" ht="16">
-      <c r="B4" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="9">
-        <v>3.9</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>279</v>
-      </c>
-    </row>
     <row r="5" spans="2:9" ht="16">
       <c r="B5" s="8" t="s">
         <v>70</v>
@@ -30125,79 +30800,8 @@
       </c>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" spans="2:9" ht="16">
-      <c r="B7" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="9">
-        <v>3.9</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="21"/>
-    </row>
-    <row r="8" spans="2:9" ht="16">
-      <c r="B8" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="9">
-        <v>3.9</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>48</v>
-      </c>
+    <row r="8" spans="2:9">
       <c r="I8" s="5"/>
-    </row>
-    <row r="9" spans="2:9" ht="16">
-      <c r="B9" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="9">
-        <v>3.9</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="I9" s="21" t="s">
-        <v>279</v>
-      </c>
     </row>
     <row r="10" spans="2:9" ht="16">
       <c r="B10" s="8" t="s">
@@ -30421,52 +31025,6 @@
       </c>
       <c r="I18" s="21"/>
     </row>
-    <row r="19" spans="2:9" ht="16">
-      <c r="B19" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="12"/>
-      <c r="I19" s="5"/>
-    </row>
-    <row r="20" spans="2:9" ht="16">
-      <c r="B20" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="9">
-        <v>2.9</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="12"/>
-      <c r="I20" s="21" t="s">
-        <v>275</v>
-      </c>
-    </row>
     <row r="21" spans="2:9" ht="16">
       <c r="B21" s="8" t="s">
         <v>183</v>
@@ -30513,28 +31071,6 @@
         <v>277</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="16">
-      <c r="B23" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="9">
-        <v>2.9</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="H23" s="12"/>
-      <c r="I23" s="5"/>
-    </row>
     <row r="24" spans="2:9" ht="16">
       <c r="B24" s="8" t="s">
         <v>124</v>
@@ -30689,56 +31225,6 @@
       <c r="H30" s="12"/>
       <c r="I30" s="21" t="s">
         <v>276</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" ht="16">
-      <c r="B31" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="9">
-        <v>3.9</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="H31" s="12"/>
-      <c r="I31" s="21" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" ht="16">
-      <c r="B32" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="9">
-        <v>3.9</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I32" s="21" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="16">

--- a/data/CaterNow_Data_master.xlsx
+++ b/data/CaterNow_Data_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benedicthorbelt/Documents/Github/uni-caternow-booking-service/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE3C7AF-FB2A-734C-A38D-24B4260D9B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7672173-3921-8F49-8199-70875204C2A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="160" yWindow="940" windowWidth="25180" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Desserts" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MainData!$B$1:$P$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MainData!$B$1:$P$144</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2863,7 +2863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X930"/>
@@ -2995,7 +2995,7 @@
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
     </row>
-    <row r="3" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="3" spans="1:24" ht="13.75" customHeight="1">
       <c r="A3" s="31">
         <v>102</v>
       </c>
@@ -3043,7 +3043,7 @@
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
     </row>
-    <row r="4" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="4" spans="1:24" ht="13.75" customHeight="1">
       <c r="A4" s="31">
         <v>103</v>
       </c>
@@ -3097,7 +3097,7 @@
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
     </row>
-    <row r="5" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="5" spans="1:24" ht="13.75" customHeight="1">
       <c r="A5" s="31">
         <v>104</v>
       </c>
@@ -3151,7 +3151,7 @@
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
     </row>
-    <row r="6" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="6" spans="1:24" ht="13.75" customHeight="1">
       <c r="A6" s="31">
         <v>105</v>
       </c>
@@ -3205,7 +3205,7 @@
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
     </row>
-    <row r="7" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="7" spans="1:24" ht="13.75" customHeight="1">
       <c r="A7" s="31">
         <v>106</v>
       </c>
@@ -3259,7 +3259,7 @@
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
     </row>
-    <row r="8" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="8" spans="1:24" ht="13.75" customHeight="1">
       <c r="A8" s="31">
         <v>107</v>
       </c>
@@ -3313,7 +3313,7 @@
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
     </row>
-    <row r="9" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="9" spans="1:24" ht="13.75" customHeight="1">
       <c r="A9" s="31">
         <v>108</v>
       </c>
@@ -3365,7 +3365,7 @@
       <c r="W9" s="5"/>
       <c r="X9" s="5"/>
     </row>
-    <row r="10" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="10" spans="1:24" ht="13.75" customHeight="1">
       <c r="A10" s="31">
         <v>109</v>
       </c>
@@ -3419,7 +3419,7 @@
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
     </row>
-    <row r="11" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="11" spans="1:24" ht="13.75" customHeight="1">
       <c r="A11" s="31">
         <v>110</v>
       </c>
@@ -3469,7 +3469,7 @@
       <c r="W11" s="5"/>
       <c r="X11" s="5"/>
     </row>
-    <row r="12" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="12" spans="1:24" ht="13.75" customHeight="1">
       <c r="A12" s="31">
         <v>111</v>
       </c>
@@ -3519,7 +3519,7 @@
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
     </row>
-    <row r="13" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="13" spans="1:24" ht="13.75" customHeight="1">
       <c r="A13" s="31">
         <v>112</v>
       </c>
@@ -3569,7 +3569,7 @@
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
     </row>
-    <row r="14" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="14" spans="1:24" ht="13.75" customHeight="1">
       <c r="A14" s="31">
         <v>113</v>
       </c>
@@ -3621,7 +3621,7 @@
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
     </row>
-    <row r="15" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="15" spans="1:24" ht="13.75" customHeight="1">
       <c r="A15" s="31">
         <v>114</v>
       </c>
@@ -3671,7 +3671,7 @@
       <c r="W15" s="5"/>
       <c r="X15" s="5"/>
     </row>
-    <row r="16" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="16" spans="1:24" ht="13.75" customHeight="1">
       <c r="A16" s="31">
         <v>115</v>
       </c>
@@ -3721,7 +3721,7 @@
       <c r="W16" s="5"/>
       <c r="X16" s="5"/>
     </row>
-    <row r="17" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="17" spans="1:24" ht="13.75" customHeight="1">
       <c r="A17" s="31">
         <v>116</v>
       </c>
@@ -3773,7 +3773,7 @@
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
     </row>
-    <row r="18" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="18" spans="1:24" ht="13.75" customHeight="1">
       <c r="A18" s="31">
         <v>117</v>
       </c>
@@ -3827,7 +3827,7 @@
       <c r="W18" s="5"/>
       <c r="X18" s="5"/>
     </row>
-    <row r="19" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="19" spans="1:24" ht="13.75" customHeight="1">
       <c r="A19" s="31">
         <v>118</v>
       </c>
@@ -3881,7 +3881,7 @@
       <c r="W19" s="5"/>
       <c r="X19" s="5"/>
     </row>
-    <row r="20" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="20" spans="1:24" ht="13.75" customHeight="1">
       <c r="A20" s="31">
         <v>119</v>
       </c>
@@ -3933,7 +3933,7 @@
       <c r="W20" s="5"/>
       <c r="X20" s="5"/>
     </row>
-    <row r="21" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="21" spans="1:24" ht="13.75" customHeight="1">
       <c r="A21" s="31">
         <v>120</v>
       </c>
@@ -3987,7 +3987,7 @@
       <c r="W21" s="5"/>
       <c r="X21" s="5"/>
     </row>
-    <row r="22" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="22" spans="1:24" ht="13.75" customHeight="1">
       <c r="A22" s="31">
         <v>121</v>
       </c>
@@ -4041,7 +4041,7 @@
       <c r="W22" s="5"/>
       <c r="X22" s="5"/>
     </row>
-    <row r="23" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="23" spans="1:24" ht="13.75" customHeight="1">
       <c r="A23" s="31">
         <v>122</v>
       </c>
@@ -4093,7 +4093,7 @@
       <c r="W23" s="5"/>
       <c r="X23" s="5"/>
     </row>
-    <row r="24" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="24" spans="1:24" ht="13.75" customHeight="1">
       <c r="A24" s="31">
         <v>123</v>
       </c>
@@ -4147,7 +4147,7 @@
       <c r="W24" s="5"/>
       <c r="X24" s="5"/>
     </row>
-    <row r="25" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="25" spans="1:24" ht="13.75" customHeight="1">
       <c r="A25" s="31">
         <v>124</v>
       </c>
@@ -4201,7 +4201,7 @@
       <c r="W25" s="5"/>
       <c r="X25" s="5"/>
     </row>
-    <row r="26" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="26" spans="1:24" ht="13.75" customHeight="1">
       <c r="A26" s="31">
         <v>125</v>
       </c>
@@ -4255,7 +4255,7 @@
       <c r="W26" s="5"/>
       <c r="X26" s="5"/>
     </row>
-    <row r="27" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="27" spans="1:24" ht="13.75" customHeight="1">
       <c r="A27" s="31">
         <v>126</v>
       </c>
@@ -4309,7 +4309,7 @@
       <c r="W27" s="5"/>
       <c r="X27" s="5"/>
     </row>
-    <row r="28" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="28" spans="1:24" ht="13.75" customHeight="1">
       <c r="A28" s="31">
         <v>127</v>
       </c>
@@ -4363,7 +4363,7 @@
       <c r="W28" s="5"/>
       <c r="X28" s="5"/>
     </row>
-    <row r="29" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="29" spans="1:24" ht="13.75" customHeight="1">
       <c r="A29" s="31">
         <v>128</v>
       </c>
@@ -4417,7 +4417,7 @@
       <c r="W29" s="5"/>
       <c r="X29" s="5"/>
     </row>
-    <row r="30" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="30" spans="1:24" ht="13.75" customHeight="1">
       <c r="A30" s="31">
         <v>129</v>
       </c>
@@ -4839,7 +4839,7 @@
       <c r="W37" s="5"/>
       <c r="X37" s="5"/>
     </row>
-    <row r="38" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="38" spans="1:24" ht="13.75" customHeight="1">
       <c r="A38" s="31">
         <v>137</v>
       </c>
@@ -4891,7 +4891,7 @@
       <c r="W38" s="5"/>
       <c r="X38" s="5"/>
     </row>
-    <row r="39" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="39" spans="1:24" ht="13.75" customHeight="1">
       <c r="A39" s="31">
         <v>138</v>
       </c>
@@ -4943,7 +4943,7 @@
       <c r="W39" s="5"/>
       <c r="X39" s="5"/>
     </row>
-    <row r="40" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="40" spans="1:24" ht="13.75" customHeight="1">
       <c r="A40" s="31">
         <v>139</v>
       </c>
@@ -4997,7 +4997,7 @@
       <c r="W40" s="5"/>
       <c r="X40" s="5"/>
     </row>
-    <row r="41" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="41" spans="1:24" ht="13.75" customHeight="1">
       <c r="A41" s="31">
         <v>140</v>
       </c>
@@ -5049,7 +5049,7 @@
       <c r="W41" s="5"/>
       <c r="X41" s="5"/>
     </row>
-    <row r="42" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="42" spans="1:24" ht="13.75" customHeight="1">
       <c r="A42" s="31">
         <v>141</v>
       </c>
@@ -5099,7 +5099,7 @@
       <c r="W42" s="5"/>
       <c r="X42" s="5"/>
     </row>
-    <row r="43" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="43" spans="1:24" ht="13.75" customHeight="1">
       <c r="A43" s="31">
         <v>142</v>
       </c>
@@ -5151,7 +5151,7 @@
       <c r="W43" s="5"/>
       <c r="X43" s="5"/>
     </row>
-    <row r="44" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="44" spans="1:24" ht="13.75" customHeight="1">
       <c r="A44" s="31">
         <v>143</v>
       </c>
@@ -5201,7 +5201,7 @@
       <c r="W44" s="5"/>
       <c r="X44" s="5"/>
     </row>
-    <row r="45" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="45" spans="1:24" ht="13.75" customHeight="1">
       <c r="A45" s="31">
         <v>144</v>
       </c>
@@ -5409,7 +5409,7 @@
       <c r="W48" s="5"/>
       <c r="X48" s="5"/>
     </row>
-    <row r="49" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="49" spans="1:24" ht="13.75" customHeight="1">
       <c r="A49" s="31">
         <v>148</v>
       </c>
@@ -5461,7 +5461,7 @@
       <c r="W49" s="5"/>
       <c r="X49" s="5"/>
     </row>
-    <row r="50" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="50" spans="1:24" ht="13.75" customHeight="1">
       <c r="A50" s="31">
         <v>149</v>
       </c>
@@ -5513,7 +5513,7 @@
       <c r="W50" s="5"/>
       <c r="X50" s="5"/>
     </row>
-    <row r="51" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="51" spans="1:24" ht="13.75" customHeight="1">
       <c r="A51" s="31">
         <v>150</v>
       </c>
@@ -5565,7 +5565,7 @@
       <c r="W51" s="5"/>
       <c r="X51" s="5"/>
     </row>
-    <row r="52" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="52" spans="1:24" ht="13.75" customHeight="1">
       <c r="A52" s="31">
         <v>151</v>
       </c>
@@ -5617,7 +5617,7 @@
       <c r="W52" s="5"/>
       <c r="X52" s="5"/>
     </row>
-    <row r="53" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="53" spans="1:24" ht="15.75" customHeight="1">
       <c r="A53" s="31">
         <v>152</v>
       </c>
@@ -5659,7 +5659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="54" spans="1:24" ht="15.75" customHeight="1">
       <c r="A54" s="31">
         <v>153</v>
       </c>
@@ -5701,7 +5701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="55" spans="1:24" ht="15.75" customHeight="1">
       <c r="A55" s="31">
         <v>154</v>
       </c>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="56" spans="1:24" ht="15.75" customHeight="1">
       <c r="A56" s="31">
         <v>155</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="57" spans="1:24" ht="15.75" customHeight="1">
       <c r="A57" s="31">
         <v>156</v>
       </c>
@@ -5825,7 +5825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="58" spans="1:24" ht="15.75" customHeight="1">
       <c r="A58" s="31">
         <v>157</v>
       </c>
@@ -5867,7 +5867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="59" spans="1:24" ht="15.75" customHeight="1">
       <c r="A59" s="31">
         <v>158</v>
       </c>
@@ -5995,7 +5995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="62" spans="1:24" ht="15.75" customHeight="1">
       <c r="A62" s="31">
         <v>161</v>
       </c>
@@ -6037,7 +6037,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="63" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="63" spans="1:24" ht="15.75" customHeight="1">
       <c r="A63" s="31">
         <v>162</v>
       </c>
@@ -6077,7 +6077,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="64" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="64" spans="1:24" ht="15.75" customHeight="1">
       <c r="A64" s="31">
         <v>163</v>
       </c>
@@ -6119,7 +6119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="65" spans="1:24" ht="13.75" customHeight="1">
       <c r="A65" s="31">
         <v>164</v>
       </c>
@@ -6171,7 +6171,7 @@
       <c r="W65" s="5"/>
       <c r="X65" s="5"/>
     </row>
-    <row r="66" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="66" spans="1:24" ht="13.75" customHeight="1">
       <c r="A66" s="31">
         <v>165</v>
       </c>
@@ -6223,7 +6223,7 @@
       <c r="W66" s="5"/>
       <c r="X66" s="5"/>
     </row>
-    <row r="67" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="67" spans="1:24" ht="13.75" customHeight="1">
       <c r="A67" s="31">
         <v>166</v>
       </c>
@@ -6275,7 +6275,7 @@
       <c r="W67" s="5"/>
       <c r="X67" s="5"/>
     </row>
-    <row r="68" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="68" spans="1:24" ht="13.75" customHeight="1">
       <c r="A68" s="31">
         <v>167</v>
       </c>
@@ -6327,7 +6327,7 @@
       <c r="W68" s="5"/>
       <c r="X68" s="5"/>
     </row>
-    <row r="69" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="69" spans="1:24" ht="13.75" customHeight="1">
       <c r="A69" s="31">
         <v>168</v>
       </c>
@@ -6379,7 +6379,7 @@
       <c r="W69" s="5"/>
       <c r="X69" s="5"/>
     </row>
-    <row r="70" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="70" spans="1:24" ht="13.75" customHeight="1">
       <c r="A70" s="31">
         <v>169</v>
       </c>
@@ -6431,7 +6431,7 @@
       <c r="W70" s="5"/>
       <c r="X70" s="5"/>
     </row>
-    <row r="71" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="71" spans="1:24" ht="13.75" customHeight="1">
       <c r="A71" s="31">
         <v>170</v>
       </c>
@@ -6483,7 +6483,7 @@
       <c r="W71" s="5"/>
       <c r="X71" s="5"/>
     </row>
-    <row r="72" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="72" spans="1:24" ht="13.75" customHeight="1">
       <c r="A72" s="31">
         <v>171</v>
       </c>
@@ -6535,7 +6535,7 @@
       <c r="W72" s="5"/>
       <c r="X72" s="5"/>
     </row>
-    <row r="73" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="73" spans="1:24" ht="13.75" customHeight="1">
       <c r="A73" s="31">
         <v>172</v>
       </c>
@@ -6587,7 +6587,7 @@
       <c r="W73" s="5"/>
       <c r="X73" s="5"/>
     </row>
-    <row r="74" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="74" spans="1:24" ht="13.75" customHeight="1">
       <c r="A74" s="31">
         <v>173</v>
       </c>
@@ -6639,7 +6639,7 @@
       <c r="W74" s="5"/>
       <c r="X74" s="5"/>
     </row>
-    <row r="75" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="75" spans="1:24" ht="13.75" customHeight="1">
       <c r="A75" s="31">
         <v>174</v>
       </c>
@@ -6691,7 +6691,7 @@
       <c r="W75" s="5"/>
       <c r="X75" s="5"/>
     </row>
-    <row r="76" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="76" spans="1:24" ht="13.75" customHeight="1">
       <c r="A76" s="31">
         <v>175</v>
       </c>
@@ -6743,7 +6743,7 @@
       <c r="W76" s="5"/>
       <c r="X76" s="5"/>
     </row>
-    <row r="77" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="77" spans="1:24" ht="13.75" customHeight="1">
       <c r="A77" s="31">
         <v>176</v>
       </c>
@@ -6795,7 +6795,7 @@
       <c r="W77" s="5"/>
       <c r="X77" s="5"/>
     </row>
-    <row r="78" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="78" spans="1:24" ht="13.75" customHeight="1">
       <c r="A78" s="31">
         <v>177</v>
       </c>
@@ -6847,7 +6847,7 @@
       <c r="W78" s="5"/>
       <c r="X78" s="5"/>
     </row>
-    <row r="79" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="79" spans="1:24" ht="13.75" customHeight="1">
       <c r="A79" s="31">
         <v>178</v>
       </c>
@@ -6899,7 +6899,7 @@
       <c r="W79" s="5"/>
       <c r="X79" s="5"/>
     </row>
-    <row r="80" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="80" spans="1:24" ht="13.75" customHeight="1">
       <c r="A80" s="31">
         <v>179</v>
       </c>
@@ -6953,7 +6953,7 @@
       <c r="W80" s="5"/>
       <c r="X80" s="5"/>
     </row>
-    <row r="81" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="81" spans="1:24" ht="13.75" customHeight="1">
       <c r="A81" s="31">
         <v>180</v>
       </c>
@@ -7007,7 +7007,7 @@
       <c r="W81" s="5"/>
       <c r="X81" s="5"/>
     </row>
-    <row r="82" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="82" spans="1:24" ht="13.75" customHeight="1">
       <c r="A82" s="31">
         <v>181</v>
       </c>
@@ -7059,7 +7059,7 @@
       <c r="W82" s="5"/>
       <c r="X82" s="5"/>
     </row>
-    <row r="83" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="83" spans="1:24" ht="13.75" customHeight="1">
       <c r="A83" s="31">
         <v>182</v>
       </c>
@@ -7111,7 +7111,7 @@
       <c r="W83" s="5"/>
       <c r="X83" s="5"/>
     </row>
-    <row r="84" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="84" spans="1:24" ht="13.75" customHeight="1">
       <c r="A84" s="31">
         <v>183</v>
       </c>
@@ -7163,7 +7163,7 @@
       <c r="W84" s="5"/>
       <c r="X84" s="5"/>
     </row>
-    <row r="85" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="85" spans="1:24" ht="13.75" customHeight="1">
       <c r="A85" s="31">
         <v>184</v>
       </c>
@@ -7215,7 +7215,7 @@
       <c r="W85" s="5"/>
       <c r="X85" s="5"/>
     </row>
-    <row r="86" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="86" spans="1:24" ht="13.75" customHeight="1">
       <c r="A86" s="31">
         <v>185</v>
       </c>
@@ -7265,7 +7265,7 @@
       <c r="W86" s="5"/>
       <c r="X86" s="5"/>
     </row>
-    <row r="87" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="87" spans="1:24" ht="13.75" customHeight="1">
       <c r="A87" s="31">
         <v>186</v>
       </c>
@@ -7315,7 +7315,7 @@
       <c r="W87" s="5"/>
       <c r="X87" s="5"/>
     </row>
-    <row r="88" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="88" spans="1:24" ht="13.75" customHeight="1">
       <c r="A88" s="31">
         <v>187</v>
       </c>
@@ -7367,7 +7367,7 @@
       <c r="W88" s="5"/>
       <c r="X88" s="5"/>
     </row>
-    <row r="89" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="89" spans="1:24" ht="13.75" customHeight="1">
       <c r="A89" s="31">
         <v>188</v>
       </c>
@@ -7419,7 +7419,7 @@
       <c r="W89" s="5"/>
       <c r="X89" s="5"/>
     </row>
-    <row r="90" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="90" spans="1:24" ht="13.75" customHeight="1">
       <c r="A90" s="31">
         <v>189</v>
       </c>
@@ -7471,7 +7471,7 @@
       <c r="W90" s="5"/>
       <c r="X90" s="5"/>
     </row>
-    <row r="91" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="91" spans="1:24" ht="13.75" customHeight="1">
       <c r="A91" s="31">
         <v>190</v>
       </c>
@@ -7523,7 +7523,7 @@
       <c r="W91" s="5"/>
       <c r="X91" s="5"/>
     </row>
-    <row r="92" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="92" spans="1:24" ht="13.75" customHeight="1">
       <c r="A92" s="31">
         <v>191</v>
       </c>
@@ -7575,7 +7575,7 @@
       <c r="W92" s="5"/>
       <c r="X92" s="5"/>
     </row>
-    <row r="93" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="93" spans="1:24" ht="13.75" customHeight="1">
       <c r="A93" s="31">
         <v>192</v>
       </c>
@@ -7627,7 +7627,7 @@
       <c r="W93" s="5"/>
       <c r="X93" s="5"/>
     </row>
-    <row r="94" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="94" spans="1:24" ht="13.75" customHeight="1">
       <c r="A94" s="31">
         <v>193</v>
       </c>
@@ -7679,7 +7679,7 @@
       <c r="W94" s="5"/>
       <c r="X94" s="5"/>
     </row>
-    <row r="95" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="95" spans="1:24" ht="13.75" customHeight="1">
       <c r="A95" s="31">
         <v>194</v>
       </c>
@@ -7729,7 +7729,7 @@
       <c r="W95" s="5"/>
       <c r="X95" s="5"/>
     </row>
-    <row r="96" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="96" spans="1:24" ht="13.75" customHeight="1">
       <c r="A96" s="31">
         <v>195</v>
       </c>
@@ -7781,7 +7781,7 @@
       <c r="W96" s="5"/>
       <c r="X96" s="5"/>
     </row>
-    <row r="97" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="97" spans="1:24" ht="13.75" customHeight="1">
       <c r="A97" s="31">
         <v>196</v>
       </c>
@@ -7833,7 +7833,7 @@
       <c r="W97" s="5"/>
       <c r="X97" s="5"/>
     </row>
-    <row r="98" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="98" spans="1:24" ht="13.75" customHeight="1">
       <c r="A98" s="31">
         <v>197</v>
       </c>
@@ -7885,7 +7885,7 @@
       <c r="W98" s="5"/>
       <c r="X98" s="5"/>
     </row>
-    <row r="99" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="99" spans="1:24" ht="13.75" customHeight="1">
       <c r="A99" s="31">
         <v>198</v>
       </c>
@@ -7937,7 +7937,7 @@
       <c r="W99" s="5"/>
       <c r="X99" s="5"/>
     </row>
-    <row r="100" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="100" spans="1:24" ht="13.75" customHeight="1">
       <c r="A100" s="31">
         <v>199</v>
       </c>
@@ -7989,7 +7989,7 @@
       <c r="W100" s="5"/>
       <c r="X100" s="5"/>
     </row>
-    <row r="101" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="101" spans="1:24" ht="13.75" customHeight="1">
       <c r="A101" s="31">
         <v>200</v>
       </c>
@@ -8041,7 +8041,7 @@
       <c r="W101" s="5"/>
       <c r="X101" s="5"/>
     </row>
-    <row r="102" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="102" spans="1:24" ht="13.75" customHeight="1">
       <c r="A102" s="31">
         <v>201</v>
       </c>
@@ -8093,7 +8093,7 @@
       <c r="W102" s="5"/>
       <c r="X102" s="5"/>
     </row>
-    <row r="103" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="103" spans="1:24" ht="13.75" customHeight="1">
       <c r="A103" s="31">
         <v>202</v>
       </c>
@@ -8145,7 +8145,7 @@
       <c r="W103" s="5"/>
       <c r="X103" s="5"/>
     </row>
-    <row r="104" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="104" spans="1:24" ht="13.75" customHeight="1">
       <c r="A104" s="31">
         <v>203</v>
       </c>
@@ -8197,7 +8197,7 @@
       <c r="W104" s="5"/>
       <c r="X104" s="5"/>
     </row>
-    <row r="105" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="105" spans="1:24" ht="13.75" customHeight="1">
       <c r="A105" s="31">
         <v>204</v>
       </c>
@@ -8247,7 +8247,7 @@
       <c r="W105" s="5"/>
       <c r="X105" s="5"/>
     </row>
-    <row r="106" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="106" spans="1:24" ht="13.75" customHeight="1">
       <c r="A106" s="31">
         <v>205</v>
       </c>
@@ -8297,7 +8297,7 @@
       <c r="W106" s="5"/>
       <c r="X106" s="5"/>
     </row>
-    <row r="107" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="107" spans="1:24" ht="13.75" customHeight="1">
       <c r="A107" s="31">
         <v>206</v>
       </c>
@@ -8349,7 +8349,7 @@
       <c r="W107" s="5"/>
       <c r="X107" s="5"/>
     </row>
-    <row r="108" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="108" spans="1:24" ht="13.75" customHeight="1">
       <c r="A108" s="31">
         <v>207</v>
       </c>
@@ -8401,7 +8401,7 @@
       <c r="W108" s="5"/>
       <c r="X108" s="5"/>
     </row>
-    <row r="109" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="109" spans="1:24" ht="13.75" customHeight="1">
       <c r="A109" s="31">
         <v>208</v>
       </c>
@@ -8453,7 +8453,7 @@
       <c r="W109" s="5"/>
       <c r="X109" s="5"/>
     </row>
-    <row r="110" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="110" spans="1:24" ht="13.75" customHeight="1">
       <c r="A110" s="31">
         <v>209</v>
       </c>
@@ -8505,7 +8505,7 @@
       <c r="W110" s="5"/>
       <c r="X110" s="5"/>
     </row>
-    <row r="111" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="111" spans="1:24" ht="13.75" customHeight="1">
       <c r="A111" s="31">
         <v>210</v>
       </c>
@@ -8557,7 +8557,7 @@
       <c r="W111" s="5"/>
       <c r="X111" s="5"/>
     </row>
-    <row r="112" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="112" spans="1:24" ht="13.75" customHeight="1">
       <c r="A112" s="31">
         <v>211</v>
       </c>
@@ -8609,7 +8609,7 @@
       <c r="W112" s="5"/>
       <c r="X112" s="5"/>
     </row>
-    <row r="113" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="113" spans="1:24" ht="13.75" customHeight="1">
       <c r="A113" s="31">
         <v>212</v>
       </c>
@@ -8661,7 +8661,7 @@
       <c r="W113" s="5"/>
       <c r="X113" s="5"/>
     </row>
-    <row r="114" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="114" spans="1:24" ht="13.75" customHeight="1">
       <c r="A114" s="31">
         <v>213</v>
       </c>
@@ -8713,7 +8713,7 @@
       <c r="W114" s="5"/>
       <c r="X114" s="5"/>
     </row>
-    <row r="115" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="115" spans="1:24" ht="13.75" customHeight="1">
       <c r="A115" s="31">
         <v>214</v>
       </c>
@@ -8765,7 +8765,7 @@
       <c r="W115" s="5"/>
       <c r="X115" s="5"/>
     </row>
-    <row r="116" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="116" spans="1:24" ht="13.75" customHeight="1">
       <c r="A116" s="31">
         <v>215</v>
       </c>
@@ -8817,7 +8817,7 @@
       <c r="W116" s="5"/>
       <c r="X116" s="5"/>
     </row>
-    <row r="117" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="117" spans="1:24" ht="13.75" customHeight="1">
       <c r="A117" s="31">
         <v>216</v>
       </c>
@@ -8869,7 +8869,7 @@
       <c r="W117" s="5"/>
       <c r="X117" s="5"/>
     </row>
-    <row r="118" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="118" spans="1:24" ht="13.75" customHeight="1">
       <c r="A118" s="31">
         <v>217</v>
       </c>
@@ -8921,7 +8921,7 @@
       <c r="W118" s="5"/>
       <c r="X118" s="5"/>
     </row>
-    <row r="119" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="119" spans="1:24" ht="13.75" customHeight="1">
       <c r="A119" s="31">
         <v>218</v>
       </c>
@@ -8971,7 +8971,7 @@
       <c r="W119" s="5"/>
       <c r="X119" s="5"/>
     </row>
-    <row r="120" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="120" spans="1:24" ht="13.75" customHeight="1">
       <c r="A120" s="31">
         <v>219</v>
       </c>
@@ -9021,7 +9021,7 @@
       <c r="W120" s="5"/>
       <c r="X120" s="5"/>
     </row>
-    <row r="121" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="121" spans="1:24" ht="13.75" customHeight="1">
       <c r="A121" s="31">
         <v>220</v>
       </c>
@@ -9071,7 +9071,7 @@
       <c r="W121" s="5"/>
       <c r="X121" s="5"/>
     </row>
-    <row r="122" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="122" spans="1:24" ht="13.75" customHeight="1">
       <c r="A122" s="31">
         <v>221</v>
       </c>
@@ -9121,7 +9121,7 @@
       <c r="W122" s="5"/>
       <c r="X122" s="5"/>
     </row>
-    <row r="123" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="123" spans="1:24" ht="13.75" customHeight="1">
       <c r="A123" s="31">
         <v>222</v>
       </c>
@@ -9173,7 +9173,7 @@
       <c r="W123" s="5"/>
       <c r="X123" s="5"/>
     </row>
-    <row r="124" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="124" spans="1:24" ht="13.75" customHeight="1">
       <c r="A124" s="31">
         <v>223</v>
       </c>
@@ -9225,7 +9225,7 @@
       <c r="W124" s="5"/>
       <c r="X124" s="5"/>
     </row>
-    <row r="125" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="125" spans="1:24" ht="13.75" customHeight="1">
       <c r="A125" s="31">
         <v>224</v>
       </c>
@@ -9277,7 +9277,7 @@
       <c r="W125" s="5"/>
       <c r="X125" s="5"/>
     </row>
-    <row r="126" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="126" spans="1:24" ht="13.75" customHeight="1">
       <c r="A126" s="31">
         <v>225</v>
       </c>
@@ -9327,7 +9327,7 @@
       <c r="W126" s="5"/>
       <c r="X126" s="5"/>
     </row>
-    <row r="127" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="127" spans="1:24" ht="13.75" customHeight="1">
       <c r="A127" s="31">
         <v>226</v>
       </c>
@@ -9377,7 +9377,7 @@
       <c r="W127" s="5"/>
       <c r="X127" s="5"/>
     </row>
-    <row r="128" spans="1:24" ht="13.75" hidden="1" customHeight="1">
+    <row r="128" spans="1:24" ht="13.75" customHeight="1">
       <c r="A128" s="31">
         <v>227</v>
       </c>
@@ -9430,7 +9430,9 @@
       <c r="X128" s="5"/>
     </row>
     <row r="129" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A129" s="9"/>
+      <c r="A129" s="31">
+        <v>228</v>
+      </c>
       <c r="B129" s="8" t="s">
         <v>78</v>
       </c>
@@ -9482,7 +9484,9 @@
       <c r="X129" s="5"/>
     </row>
     <row r="130" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A130" s="9"/>
+      <c r="A130" s="31">
+        <v>229</v>
+      </c>
       <c r="B130" s="8" t="s">
         <v>76</v>
       </c>
@@ -9534,7 +9538,9 @@
       <c r="X130" s="5"/>
     </row>
     <row r="131" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A131" s="9"/>
+      <c r="A131" s="31">
+        <v>230</v>
+      </c>
       <c r="B131" s="8" t="s">
         <v>184</v>
       </c>
@@ -9584,7 +9590,9 @@
       <c r="X131" s="5"/>
     </row>
     <row r="132" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A132" s="9"/>
+      <c r="A132" s="31">
+        <v>231</v>
+      </c>
       <c r="B132" s="8" t="s">
         <v>150</v>
       </c>
@@ -9636,7 +9644,9 @@
       <c r="X132" s="5"/>
     </row>
     <row r="133" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A133" s="9"/>
+      <c r="A133" s="31">
+        <v>232</v>
+      </c>
       <c r="B133" s="8" t="s">
         <v>147</v>
       </c>
@@ -9686,7 +9696,9 @@
       <c r="X133" s="5"/>
     </row>
     <row r="134" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A134" s="9"/>
+      <c r="A134" s="31">
+        <v>233</v>
+      </c>
       <c r="B134" s="8" t="s">
         <v>74</v>
       </c>
@@ -9738,7 +9750,9 @@
       <c r="X134" s="5"/>
     </row>
     <row r="135" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A135" s="9"/>
+      <c r="A135" s="31">
+        <v>234</v>
+      </c>
       <c r="B135" s="8" t="s">
         <v>68</v>
       </c>
@@ -9790,7 +9804,9 @@
       <c r="X135" s="5"/>
     </row>
     <row r="136" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A136" s="9"/>
+      <c r="A136" s="31">
+        <v>235</v>
+      </c>
       <c r="B136" s="8" t="s">
         <v>190</v>
       </c>
@@ -9840,7 +9856,9 @@
       <c r="X136" s="5"/>
     </row>
     <row r="137" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A137"/>
+      <c r="A137" s="31">
+        <v>236</v>
+      </c>
       <c r="B137" s="8" t="s">
         <v>191</v>
       </c>
@@ -9890,7 +9908,9 @@
       <c r="X137" s="5"/>
     </row>
     <row r="138" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A138" s="9"/>
+      <c r="A138" s="31">
+        <v>237</v>
+      </c>
       <c r="B138" s="8" t="s">
         <v>497</v>
       </c>
@@ -9942,7 +9962,9 @@
       <c r="X138" s="5"/>
     </row>
     <row r="139" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A139" s="9"/>
+      <c r="A139" s="31">
+        <v>238</v>
+      </c>
       <c r="B139" s="8" t="s">
         <v>499</v>
       </c>
@@ -9994,7 +10016,9 @@
       <c r="X139" s="5"/>
     </row>
     <row r="140" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A140" s="9"/>
+      <c r="A140" s="31">
+        <v>239</v>
+      </c>
       <c r="B140" s="8" t="s">
         <v>501</v>
       </c>
@@ -10044,7 +10068,9 @@
       <c r="X140" s="5"/>
     </row>
     <row r="141" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A141" s="9"/>
+      <c r="A141" s="31">
+        <v>240</v>
+      </c>
       <c r="B141" s="8" t="s">
         <v>503</v>
       </c>
@@ -10094,7 +10120,9 @@
       <c r="X141" s="5"/>
     </row>
     <row r="142" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A142" s="9"/>
+      <c r="A142" s="31">
+        <v>241</v>
+      </c>
       <c r="B142" s="8" t="s">
         <v>505</v>
       </c>
@@ -10142,7 +10170,9 @@
       <c r="X142" s="5"/>
     </row>
     <row r="143" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A143" s="9"/>
+      <c r="A143" s="31">
+        <v>242</v>
+      </c>
       <c r="B143" s="8" t="s">
         <v>507</v>
       </c>
@@ -10192,7 +10222,9 @@
       <c r="X143" s="5"/>
     </row>
     <row r="144" spans="1:24" ht="13.75" customHeight="1">
-      <c r="A144" s="9"/>
+      <c r="A144" s="31">
+        <v>243</v>
+      </c>
       <c r="B144" s="8" t="s">
         <v>509</v>
       </c>
@@ -30668,13 +30700,7 @@
       <c r="X930" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:P137" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Dessert"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B1:P144" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="J2:N144">
     <cfRule type="colorScale" priority="1">
       <colorScale>
